--- a/Input files/Database EGJA.xlsx
+++ b/Input files/Database EGJA.xlsx
@@ -1020,7 +1020,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1466,9 +1466,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1912,10 +1909,10 @@
       <c r="U1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="151" t="s">
+      <c r="V1" s="150" t="s">
         <v>211</v>
       </c>
-      <c r="W1" s="151" t="s">
+      <c r="W1" s="150" t="s">
         <v>212</v>
       </c>
       <c r="X1" s="10" t="s">
@@ -2098,10 +2095,10 @@
       <c r="U2" s="35">
         <v>1</v>
       </c>
-      <c r="V2" s="152">
+      <c r="V2" s="151">
         <v>4</v>
       </c>
-      <c r="W2" s="152">
+      <c r="W2" s="151">
         <v>2</v>
       </c>
       <c r="X2" s="39">
@@ -2280,10 +2277,10 @@
       <c r="U3" s="58">
         <v>0</v>
       </c>
-      <c r="V3" s="153">
-        <v>3</v>
-      </c>
-      <c r="W3" s="153">
+      <c r="V3" s="152">
+        <v>3</v>
+      </c>
+      <c r="W3" s="152">
         <v>1</v>
       </c>
       <c r="X3" s="52">
@@ -2422,10 +2419,10 @@
       <c r="U4" s="73">
         <v>0</v>
       </c>
-      <c r="V4" s="152">
-        <v>3</v>
-      </c>
-      <c r="W4" s="153">
+      <c r="V4" s="151">
+        <v>3</v>
+      </c>
+      <c r="W4" s="152">
         <v>1</v>
       </c>
       <c r="X4" s="52">
@@ -2604,10 +2601,10 @@
       <c r="U5" s="78">
         <v>0</v>
       </c>
-      <c r="V5" s="154">
-        <v>3</v>
-      </c>
-      <c r="W5" s="153">
+      <c r="V5" s="153">
+        <v>3</v>
+      </c>
+      <c r="W5" s="152">
         <v>1</v>
       </c>
       <c r="X5" s="52">
@@ -2778,10 +2775,10 @@
       <c r="U6" s="52">
         <v>1</v>
       </c>
-      <c r="V6" s="155">
+      <c r="V6" s="154">
         <v>4</v>
       </c>
-      <c r="W6" s="152">
+      <c r="W6" s="151">
         <v>2</v>
       </c>
       <c r="X6" s="52">
@@ -2920,10 +2917,10 @@
       <c r="U7" s="52">
         <v>0</v>
       </c>
-      <c r="V7" s="155">
-        <v>3</v>
-      </c>
-      <c r="W7" s="153">
+      <c r="V7" s="154">
+        <v>3</v>
+      </c>
+      <c r="W7" s="152">
         <v>1</v>
       </c>
       <c r="X7" s="52">
@@ -3234,10 +3231,10 @@
       <c r="U9" s="85">
         <v>0</v>
       </c>
-      <c r="V9" s="155">
-        <v>3</v>
-      </c>
-      <c r="W9" s="153">
+      <c r="V9" s="154">
+        <v>3</v>
+      </c>
+      <c r="W9" s="152">
         <v>1</v>
       </c>
       <c r="X9" s="86">
@@ -3414,10 +3411,10 @@
       <c r="U10" s="52">
         <v>0</v>
       </c>
-      <c r="V10" s="155">
+      <c r="V10" s="154">
         <v>4</v>
       </c>
-      <c r="W10" s="152">
+      <c r="W10" s="151">
         <v>2</v>
       </c>
       <c r="X10" s="52">
@@ -3598,10 +3595,10 @@
       <c r="U11" s="94">
         <v>0</v>
       </c>
-      <c r="V11" s="156">
-        <v>2</v>
-      </c>
-      <c r="W11" s="152">
+      <c r="V11" s="155">
+        <v>2</v>
+      </c>
+      <c r="W11" s="151">
         <v>0</v>
       </c>
       <c r="X11" s="39">
@@ -3784,10 +3781,10 @@
       <c r="U12" s="73">
         <v>0</v>
       </c>
-      <c r="V12" s="152">
-        <v>3</v>
-      </c>
-      <c r="W12" s="153">
+      <c r="V12" s="151">
+        <v>3</v>
+      </c>
+      <c r="W12" s="152">
         <v>1</v>
       </c>
       <c r="X12" s="52">
@@ -3904,145 +3901,145 @@
     </row>
     <row r="13" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="52">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13" s="52">
-        <v>1970</v>
+        <v>1990</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" s="72">
-        <v>71.211111111111109</v>
+        <v>77.330555555555549</v>
       </c>
       <c r="F13" s="55">
         <v>1</v>
       </c>
       <c r="G13" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="48">
+        <v>5</v>
+      </c>
+      <c r="J13" s="47">
+        <v>19.477146814404431</v>
+      </c>
+      <c r="K13" s="48">
+        <v>7.5</v>
+      </c>
+      <c r="L13" s="48">
+        <v>3</v>
+      </c>
+      <c r="M13" s="48">
+        <v>2500</v>
+      </c>
+      <c r="N13" s="48">
+        <v>1100</v>
+      </c>
+      <c r="O13" s="57">
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="P13" s="52">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="48">
         <v>4</v>
       </c>
-      <c r="J13" s="47">
-        <v>23.046874999999996</v>
-      </c>
-      <c r="K13" s="48">
-        <v>15.3</v>
-      </c>
-      <c r="L13" s="48">
+      <c r="R13" s="48">
+        <v>1</v>
+      </c>
+      <c r="S13" s="73">
+        <v>0</v>
+      </c>
+      <c r="T13" s="73">
+        <v>0</v>
+      </c>
+      <c r="U13" s="73">
+        <v>0</v>
+      </c>
+      <c r="V13" s="155">
+        <v>2</v>
+      </c>
+      <c r="W13" s="151">
+        <v>0</v>
+      </c>
+      <c r="X13" s="52">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="48">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="48">
+        <v>46</v>
+      </c>
+      <c r="AF13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="48">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="42">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="47">
         <v>5</v>
       </c>
-      <c r="M13" s="48">
-        <v>6490</v>
-      </c>
-      <c r="N13" s="48">
-        <v>2670</v>
-      </c>
-      <c r="O13" s="57">
-        <v>2.4307116104868913</v>
-      </c>
-      <c r="P13" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="73">
-        <v>2</v>
-      </c>
-      <c r="R13" s="73">
-        <v>0</v>
-      </c>
-      <c r="S13" s="73">
-        <v>1</v>
-      </c>
-      <c r="T13" s="59">
-        <v>1</v>
-      </c>
-      <c r="U13" s="73">
-        <v>0</v>
-      </c>
-      <c r="V13" s="152">
-        <v>2</v>
-      </c>
-      <c r="W13" s="152">
-        <v>0</v>
-      </c>
-      <c r="X13" s="52">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="74">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="48">
-        <v>21</v>
-      </c>
-      <c r="AF13" s="48">
+      <c r="AL13" s="48">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="48">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="52">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="48">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="48">
+        <v>2</v>
+      </c>
+      <c r="AR13" s="42">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="48">
         <v>6</v>
       </c>
-      <c r="AG13" s="48">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="48">
-        <v>1</v>
-      </c>
-      <c r="AI13" s="48">
-        <v>1</v>
-      </c>
-      <c r="AJ13" s="42">
-        <v>1</v>
-      </c>
-      <c r="AK13" s="47">
-        <v>2.8</v>
-      </c>
-      <c r="AL13" s="48">
-        <v>2</v>
-      </c>
-      <c r="AM13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="48">
-        <v>2</v>
-      </c>
-      <c r="AO13" s="48">
-        <v>1</v>
-      </c>
-      <c r="AP13" s="48">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR13" s="42">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="48">
-        <v>7</v>
-      </c>
       <c r="AT13" s="65">
         <v>0</v>
       </c>
       <c r="AU13" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV13" s="52">
         <v>0</v>
@@ -4053,14 +4050,14 @@
       <c r="AX13" s="62">
         <v>0</v>
       </c>
-      <c r="AY13" s="65">
+      <c r="AY13" s="62">
         <v>0</v>
       </c>
       <c r="AZ13" s="47">
-        <v>60</v>
+        <v>3.9</v>
       </c>
       <c r="BA13" s="47">
-        <v>60</v>
+        <v>3.9</v>
       </c>
       <c r="BB13" s="65"/>
       <c r="BC13" s="65"/>
@@ -4069,19 +4066,19 @@
         <v>41</v>
       </c>
       <c r="BF13" s="49">
-        <v>42604</v>
-      </c>
-      <c r="BG13" s="137">
-        <v>44909</v>
-      </c>
-      <c r="BH13" s="137">
-        <v>44909</v>
+        <v>42747</v>
+      </c>
+      <c r="BG13" s="135">
+        <v>42864</v>
+      </c>
+      <c r="BH13" s="135">
+        <v>42864</v>
       </c>
       <c r="BI13" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ13" s="98" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
@@ -4148,10 +4145,10 @@
       <c r="U14" s="78">
         <v>0</v>
       </c>
-      <c r="V14" s="154">
+      <c r="V14" s="153">
         <v>4</v>
       </c>
-      <c r="W14" s="152">
+      <c r="W14" s="151">
         <v>2</v>
       </c>
       <c r="X14" s="52">
@@ -4268,52 +4265,52 @@
     </row>
     <row r="15" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="52">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="52">
-        <v>1990</v>
+        <v>3009</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="72">
-        <v>77.330555555555549</v>
+        <v>67.575000000000003</v>
       </c>
       <c r="F15" s="55">
         <v>1</v>
       </c>
       <c r="G15" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="48">
         <v>0</v>
       </c>
       <c r="I15" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="47">
-        <v>19.477146814404431</v>
+        <v>22.829964328180736</v>
       </c>
       <c r="K15" s="48">
-        <v>7.5</v>
+        <v>12.6</v>
       </c>
       <c r="L15" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="48">
-        <v>2500</v>
+        <v>3840</v>
       </c>
       <c r="N15" s="48">
-        <v>1100</v>
+        <v>1450</v>
       </c>
       <c r="O15" s="57">
-        <v>2.2727272727272729</v>
+        <v>2.6482758620689655</v>
       </c>
       <c r="P15" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="48">
         <v>4</v>
@@ -4322,19 +4319,19 @@
         <v>1</v>
       </c>
       <c r="S15" s="73">
-        <v>0</v>
-      </c>
-      <c r="T15" s="73">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T15" s="59">
+        <v>1</v>
       </c>
       <c r="U15" s="73">
         <v>0</v>
       </c>
-      <c r="V15" s="156">
-        <v>2</v>
+      <c r="V15" s="151">
+        <v>3</v>
       </c>
       <c r="W15" s="152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="52">
         <v>0</v>
@@ -4346,28 +4343,28 @@
         <v>0</v>
       </c>
       <c r="AA15" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB15" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="48">
         <v>1</v>
       </c>
       <c r="AE15" s="48">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AF15" s="48">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AG15" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="48">
         <v>1</v>
@@ -4376,16 +4373,16 @@
         <v>1</v>
       </c>
       <c r="AK15" s="47">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AL15" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="48">
         <v>1</v>
       </c>
       <c r="AN15" s="52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO15" s="52">
         <v>1</v>
@@ -4394,317 +4391,275 @@
         <v>0</v>
       </c>
       <c r="AQ15" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR15" s="42">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR15" s="145">
+        <v>1</v>
       </c>
       <c r="AS15" s="48">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AT15" s="65">
         <v>0</v>
       </c>
       <c r="AU15" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX15" s="62">
-        <v>0</v>
-      </c>
-      <c r="AY15" s="62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW15" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX15" s="65">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="65">
+        <v>1</v>
       </c>
       <c r="AZ15" s="47">
-        <v>3.9</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="BA15" s="47">
-        <v>3.9</v>
-      </c>
-      <c r="BB15" s="65"/>
-      <c r="BC15" s="65"/>
-      <c r="BD15" s="65"/>
+        <v>46.8</v>
+      </c>
+      <c r="BB15" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="65">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="65">
+        <v>1</v>
+      </c>
       <c r="BE15" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF15" s="49">
-        <v>42747</v>
-      </c>
-      <c r="BG15" s="135">
-        <v>42864</v>
-      </c>
-      <c r="BH15" s="135">
-        <v>42864</v>
+        <v>42698</v>
+      </c>
+      <c r="BG15" s="134" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH15" s="137">
+        <v>44285</v>
       </c>
       <c r="BI15" s="53" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="BJ15" s="62" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="52">
-        <v>3009</v>
+        <v>3041</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="72">
-        <v>67.575000000000003</v>
+        <v>142</v>
+      </c>
+      <c r="D16" s="53">
+        <v>15989</v>
+      </c>
+      <c r="E16" s="54">
+        <v>73</v>
       </c>
       <c r="F16" s="55">
         <v>1</v>
       </c>
       <c r="G16" s="52">
-        <v>0</v>
-      </c>
-      <c r="H16" s="48">
-        <v>0</v>
-      </c>
-      <c r="I16" s="48">
-        <v>4</v>
-      </c>
-      <c r="J16" s="47">
-        <v>22.829964328180736</v>
-      </c>
-      <c r="K16" s="48">
-        <v>12.6</v>
-      </c>
-      <c r="L16" s="48">
-        <v>4</v>
-      </c>
-      <c r="M16" s="48">
-        <v>3840</v>
-      </c>
-      <c r="N16" s="48">
-        <v>1450</v>
+        <v>1</v>
+      </c>
+      <c r="H16" s="56">
+        <v>1</v>
+      </c>
+      <c r="I16" s="52">
+        <v>3</v>
+      </c>
+      <c r="J16" s="77">
+        <v>31.4</v>
+      </c>
+      <c r="K16" s="52">
+        <v>9.6</v>
+      </c>
+      <c r="L16" s="52">
+        <v>4.2</v>
+      </c>
+      <c r="M16" s="52">
+        <v>25240</v>
+      </c>
+      <c r="N16" s="52">
+        <v>1720</v>
       </c>
       <c r="O16" s="57">
-        <v>2.6482758620689655</v>
+        <v>14.67</v>
       </c>
       <c r="P16" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="48">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="78">
+        <v>3</v>
       </c>
       <c r="R16" s="48">
         <v>1</v>
       </c>
-      <c r="S16" s="73">
+      <c r="S16" s="78">
         <v>3</v>
       </c>
       <c r="T16" s="59">
         <v>1</v>
       </c>
-      <c r="U16" s="73">
-        <v>0</v>
-      </c>
-      <c r="V16" s="152">
-        <v>3</v>
-      </c>
-      <c r="W16" s="153">
+      <c r="U16" s="78">
+        <v>0</v>
+      </c>
+      <c r="V16" s="153">
+        <v>3</v>
+      </c>
+      <c r="W16" s="152">
         <v>1</v>
       </c>
       <c r="X16" s="52">
         <v>0</v>
       </c>
-      <c r="Y16" s="74">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB16" s="48">
-        <v>1</v>
+      <c r="Y16" s="52">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="52">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="52">
+        <v>3</v>
       </c>
       <c r="AC16" s="48">
         <v>0</v>
       </c>
       <c r="AD16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="48">
-        <v>28</v>
-      </c>
-      <c r="AF16" s="48">
-        <v>22</v>
-      </c>
-      <c r="AG16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AI16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="42">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="47">
-        <v>5.5</v>
-      </c>
-      <c r="AL16" s="48">
-        <v>4</v>
-      </c>
-      <c r="AM16" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="52">
-        <v>3</v>
-      </c>
-      <c r="AO16" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP16" s="48">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR16" s="145">
-        <v>1</v>
-      </c>
-      <c r="AS16" s="48">
-        <v>12</v>
-      </c>
-      <c r="AT16" s="65">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="52">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="61"/>
+      <c r="AF16" s="61"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
+      <c r="AI16" s="61"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="77">
+        <v>9</v>
+      </c>
+      <c r="AL16" s="61"/>
+      <c r="AM16" s="61"/>
+      <c r="AN16" s="61"/>
+      <c r="AO16" s="61"/>
+      <c r="AP16" s="61"/>
+      <c r="AQ16" s="61"/>
+      <c r="AR16" s="146"/>
+      <c r="AS16" s="52"/>
+      <c r="AT16" s="62"/>
+      <c r="AU16" s="63"/>
       <c r="AV16" s="52">
         <v>1</v>
       </c>
-      <c r="AW16" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX16" s="65">
-        <v>1</v>
-      </c>
-      <c r="AY16" s="65">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="47">
-        <v>32.700000000000003</v>
-      </c>
+      <c r="AW16" s="103"/>
+      <c r="AX16" s="103"/>
+      <c r="AY16" s="66">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="47"/>
       <c r="BA16" s="47">
-        <v>46.8</v>
-      </c>
-      <c r="BB16" s="65">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="65">
-        <v>1</v>
-      </c>
-      <c r="BD16" s="65">
-        <v>1</v>
-      </c>
-      <c r="BE16" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="BF16" s="49">
-        <v>42698</v>
-      </c>
-      <c r="BG16" s="134" t="s">
-        <v>96</v>
-      </c>
-      <c r="BH16" s="137">
-        <v>44285</v>
-      </c>
-      <c r="BI16" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ16" s="98" t="s">
-        <v>43</v>
+        <v>6.9666666666666668</v>
+      </c>
+      <c r="BB16" s="66"/>
+      <c r="BC16" s="66"/>
+      <c r="BD16" s="66"/>
+      <c r="BE16" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF16" s="68">
+        <v>42725</v>
+      </c>
+      <c r="BG16" s="1">
+        <v>42936</v>
+      </c>
+      <c r="BH16" s="1">
+        <v>42936</v>
+      </c>
+      <c r="BI16" s="69"/>
+      <c r="BJ16" s="79" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="52">
-        <v>3041</v>
+        <v>3599</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="53">
-        <v>15989</v>
+        <v>14944</v>
       </c>
       <c r="E17" s="54">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F17" s="55">
         <v>1</v>
       </c>
       <c r="G17" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="56">
         <v>1</v>
       </c>
-      <c r="I17" s="52">
-        <v>3</v>
+      <c r="I17" s="56">
+        <v>2</v>
       </c>
       <c r="J17" s="77">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="K17" s="52">
-        <v>9.6</v>
+        <v>12.6</v>
       </c>
       <c r="L17" s="52">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="M17" s="52">
-        <v>25240</v>
+        <v>1480</v>
       </c>
       <c r="N17" s="52">
-        <v>1720</v>
+        <v>2130</v>
       </c>
       <c r="O17" s="57">
-        <v>14.67</v>
+        <v>0.69</v>
       </c>
       <c r="P17" s="52">
         <v>1</v>
       </c>
-      <c r="Q17" s="78">
-        <v>3</v>
+      <c r="Q17" s="48">
+        <v>4</v>
       </c>
       <c r="R17" s="48">
         <v>1</v>
       </c>
       <c r="S17" s="78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" s="59">
         <v>1</v>
       </c>
       <c r="U17" s="78">
-        <v>0</v>
-      </c>
-      <c r="V17" s="154">
-        <v>3</v>
-      </c>
-      <c r="W17" s="153">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="V17" s="153">
+        <v>4</v>
+      </c>
+      <c r="W17" s="151">
+        <v>2</v>
       </c>
       <c r="X17" s="52">
         <v>0</v>
@@ -4731,8 +4686,8 @@
       <c r="AH17" s="61"/>
       <c r="AI17" s="61"/>
       <c r="AJ17" s="39"/>
-      <c r="AK17" s="77">
-        <v>9</v>
+      <c r="AK17" s="54">
+        <v>8</v>
       </c>
       <c r="AL17" s="61"/>
       <c r="AM17" s="61"/>
@@ -4749,12 +4704,12 @@
       </c>
       <c r="AW17" s="103"/>
       <c r="AX17" s="103"/>
-      <c r="AY17" s="66">
-        <v>0</v>
+      <c r="AY17" s="65">
+        <v>1</v>
       </c>
       <c r="AZ17" s="47"/>
       <c r="BA17" s="47">
-        <v>6.9666666666666668</v>
+        <v>6.7666666666666666</v>
       </c>
       <c r="BB17" s="66"/>
       <c r="BC17" s="66"/>
@@ -4763,67 +4718,67 @@
         <v>90</v>
       </c>
       <c r="BF17" s="68">
-        <v>42725</v>
-      </c>
-      <c r="BG17" s="1">
-        <v>42936</v>
-      </c>
-      <c r="BH17" s="1">
-        <v>42936</v>
+        <v>43170</v>
+      </c>
+      <c r="BG17" s="139">
+        <v>43377</v>
+      </c>
+      <c r="BH17" s="139">
+        <v>43377</v>
       </c>
       <c r="BI17" s="69"/>
-      <c r="BJ17" s="79" t="s">
-        <v>70</v>
+      <c r="BJ17" s="70" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="52">
-        <v>3599</v>
+        <v>3606</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="53">
-        <v>14944</v>
-      </c>
-      <c r="E18" s="54">
-        <v>76</v>
+      <c r="D18" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="72">
+        <v>68.108333333333334</v>
       </c>
       <c r="F18" s="55">
         <v>1</v>
       </c>
       <c r="G18" s="52">
-        <v>0</v>
-      </c>
-      <c r="H18" s="56">
+        <v>1</v>
+      </c>
+      <c r="H18" s="48">
         <v>1</v>
       </c>
       <c r="I18" s="56">
         <v>2</v>
       </c>
-      <c r="J18" s="77">
-        <v>30.8</v>
-      </c>
-      <c r="K18" s="52">
-        <v>12.6</v>
-      </c>
-      <c r="L18" s="52">
-        <v>3.6</v>
-      </c>
-      <c r="M18" s="52">
-        <v>1480</v>
-      </c>
-      <c r="N18" s="52">
-        <v>2130</v>
+      <c r="J18" s="47">
+        <v>18.426534209261334</v>
+      </c>
+      <c r="K18" s="48">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L18" s="48">
+        <v>3.5</v>
+      </c>
+      <c r="M18" s="48">
+        <v>2900</v>
+      </c>
+      <c r="N18" s="48">
+        <v>1800</v>
       </c>
       <c r="O18" s="57">
-        <v>0.69</v>
+        <v>1.6111111111111112</v>
       </c>
       <c r="P18" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="48">
         <v>4</v>
@@ -4831,33 +4786,35 @@
       <c r="R18" s="48">
         <v>1</v>
       </c>
-      <c r="S18" s="78">
+      <c r="S18" s="73">
         <v>1</v>
       </c>
       <c r="T18" s="59">
         <v>1</v>
       </c>
-      <c r="U18" s="78">
-        <v>1</v>
-      </c>
-      <c r="V18" s="154">
-        <v>4</v>
+      <c r="U18" s="73">
+        <v>0</v>
+      </c>
+      <c r="V18" s="151">
+        <v>3</v>
       </c>
       <c r="W18" s="152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X18" s="52">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="52">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="52">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="60"/>
-      <c r="AB18" s="52">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="Y18" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="48">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="48">
+        <v>1</v>
       </c>
       <c r="AC18" s="48">
         <v>0</v>
@@ -4865,72 +4822,112 @@
       <c r="AD18" s="48">
         <v>0</v>
       </c>
-      <c r="AE18" s="61"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="39"/>
-      <c r="AK18" s="54">
-        <v>8</v>
-      </c>
-      <c r="AL18" s="61"/>
-      <c r="AM18" s="61"/>
-      <c r="AN18" s="61"/>
-      <c r="AO18" s="61"/>
-      <c r="AP18" s="61"/>
-      <c r="AQ18" s="61"/>
-      <c r="AR18" s="146"/>
-      <c r="AS18" s="52"/>
-      <c r="AT18" s="62"/>
-      <c r="AU18" s="63"/>
+      <c r="AE18" s="48">
+        <v>56</v>
+      </c>
+      <c r="AF18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="42">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="47">
+        <v>3.8</v>
+      </c>
+      <c r="AL18" s="48">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="48">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="48">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="42">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="48">
+        <v>20</v>
+      </c>
+      <c r="AT18" s="62">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="52">
+        <v>0</v>
+      </c>
       <c r="AV18" s="52">
-        <v>1</v>
-      </c>
-      <c r="AW18" s="103"/>
-      <c r="AX18" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="65">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="65">
+        <v>0</v>
+      </c>
       <c r="AY18" s="65">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="47"/>
-      <c r="BA18" s="47">
-        <v>6.7666666666666666</v>
-      </c>
-      <c r="BB18" s="66"/>
-      <c r="BC18" s="66"/>
-      <c r="BD18" s="66"/>
-      <c r="BE18" s="67" t="s">
-        <v>90</v>
-      </c>
-      <c r="BF18" s="68">
-        <v>43170</v>
-      </c>
-      <c r="BG18" s="139">
-        <v>43377</v>
-      </c>
-      <c r="BH18" s="139">
-        <v>43377</v>
-      </c>
-      <c r="BI18" s="69"/>
-      <c r="BJ18" s="70" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="144">
+        <v>60</v>
+      </c>
+      <c r="BA18" s="144">
+        <v>59.966666666666669</v>
+      </c>
+      <c r="BB18" s="65"/>
+      <c r="BC18" s="65"/>
+      <c r="BD18" s="65"/>
+      <c r="BE18" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF18" s="49">
+        <v>43062</v>
+      </c>
+      <c r="BG18" s="136">
+        <v>44806</v>
+      </c>
+      <c r="BH18" s="136">
+        <v>44806</v>
+      </c>
+      <c r="BI18" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ18" s="50" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="52">
-        <v>3606</v>
+        <v>3610</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="72">
-        <v>68.108333333333334</v>
+        <v>144</v>
+      </c>
+      <c r="D19" s="69">
+        <v>16043</v>
+      </c>
+      <c r="E19" s="54">
+        <v>73</v>
       </c>
       <c r="F19" s="55">
         <v>1</v>
@@ -4938,52 +4935,52 @@
       <c r="G19" s="52">
         <v>1</v>
       </c>
-      <c r="H19" s="48">
-        <v>1</v>
+      <c r="H19" s="76">
+        <v>0</v>
       </c>
       <c r="I19" s="56">
-        <v>2</v>
-      </c>
-      <c r="J19" s="47">
-        <v>18.426534209261334</v>
-      </c>
-      <c r="K19" s="48">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L19" s="48">
-        <v>3.5</v>
-      </c>
-      <c r="M19" s="48">
-        <v>2900</v>
-      </c>
-      <c r="N19" s="48">
-        <v>1800</v>
+        <v>1</v>
+      </c>
+      <c r="J19" s="54">
+        <v>32</v>
+      </c>
+      <c r="K19" s="52">
+        <v>14.4</v>
+      </c>
+      <c r="L19" s="52">
+        <v>3.2</v>
+      </c>
+      <c r="M19" s="52">
+        <v>4020</v>
+      </c>
+      <c r="N19" s="52">
+        <v>1170</v>
       </c>
       <c r="O19" s="57">
-        <v>1.6111111111111112</v>
+        <v>3.44</v>
       </c>
       <c r="P19" s="52">
         <v>0</v>
       </c>
-      <c r="Q19" s="48">
-        <v>4</v>
+      <c r="Q19" s="74">
+        <v>3</v>
       </c>
       <c r="R19" s="48">
         <v>1</v>
       </c>
-      <c r="S19" s="73">
-        <v>1</v>
-      </c>
-      <c r="T19" s="59">
-        <v>1</v>
-      </c>
-      <c r="U19" s="73">
+      <c r="S19" s="74">
+        <v>0</v>
+      </c>
+      <c r="T19" s="73">
+        <v>0</v>
+      </c>
+      <c r="U19" s="58">
         <v>0</v>
       </c>
       <c r="V19" s="152">
         <v>3</v>
       </c>
-      <c r="W19" s="153">
+      <c r="W19" s="152">
         <v>1</v>
       </c>
       <c r="X19" s="52">
@@ -4995,11 +4992,9 @@
       <c r="Z19" s="48">
         <v>0</v>
       </c>
-      <c r="AA19" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB19" s="48">
-        <v>1</v>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="74">
+        <v>2</v>
       </c>
       <c r="AC19" s="48">
         <v>0</v>
@@ -5007,29 +5002,27 @@
       <c r="AD19" s="48">
         <v>0</v>
       </c>
-      <c r="AE19" s="48">
-        <v>56</v>
-      </c>
-      <c r="AF19" s="48">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="48">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="48">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="42">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="47">
-        <v>3.8</v>
-      </c>
-      <c r="AL19" s="48">
-        <v>2</v>
+      <c r="AE19" s="74">
+        <v>9</v>
+      </c>
+      <c r="AF19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="39"/>
+      <c r="AK19" s="72">
+        <v>6</v>
+      </c>
+      <c r="AL19" s="74">
+        <v>1</v>
       </c>
       <c r="AM19" s="48">
         <v>0</v>
@@ -5043,16 +5036,14 @@
       <c r="AP19" s="48">
         <v>0</v>
       </c>
-      <c r="AQ19" s="48">
+      <c r="AQ19" s="74">
         <v>1</v>
       </c>
       <c r="AR19" s="42">
         <v>0</v>
       </c>
-      <c r="AS19" s="48">
-        <v>20</v>
-      </c>
-      <c r="AT19" s="62">
+      <c r="AS19" s="52"/>
+      <c r="AT19" s="99">
         <v>0</v>
       </c>
       <c r="AU19" s="52">
@@ -5061,115 +5052,113 @@
       <c r="AV19" s="52">
         <v>0</v>
       </c>
-      <c r="AW19" s="65">
-        <v>0</v>
-      </c>
-      <c r="AX19" s="65">
-        <v>0</v>
+      <c r="AW19" s="99">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="62">
+        <v>1</v>
       </c>
       <c r="AY19" s="65">
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="144">
-        <v>60</v>
-      </c>
-      <c r="BA19" s="144">
-        <v>59.966666666666669</v>
-      </c>
-      <c r="BB19" s="65"/>
-      <c r="BC19" s="65"/>
-      <c r="BD19" s="65"/>
-      <c r="BE19" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="BF19" s="49">
-        <v>43062</v>
-      </c>
-      <c r="BG19" s="136">
-        <v>44806</v>
-      </c>
-      <c r="BH19" s="136">
-        <v>44806</v>
-      </c>
-      <c r="BI19" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ19" s="50" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="47">
+        <v>1.7</v>
+      </c>
+      <c r="BA19" s="47">
+        <v>1.7</v>
+      </c>
+      <c r="BB19" s="99"/>
+      <c r="BC19" s="99"/>
+      <c r="BD19" s="99"/>
+      <c r="BE19" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF19" s="101">
+        <v>43027</v>
+      </c>
+      <c r="BG19" s="139">
+        <v>43079</v>
+      </c>
+      <c r="BH19" s="139">
+        <v>43079</v>
+      </c>
+      <c r="BI19" s="101"/>
+      <c r="BJ19" s="102" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="52">
-        <v>3610</v>
+        <v>1970</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="69">
-        <v>16043</v>
-      </c>
-      <c r="E20" s="54">
-        <v>73</v>
+        <v>146</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="72">
+        <v>71.211111111111109</v>
       </c>
       <c r="F20" s="55">
         <v>1</v>
       </c>
       <c r="G20" s="52">
-        <v>1</v>
-      </c>
-      <c r="H20" s="76">
-        <v>0</v>
-      </c>
-      <c r="I20" s="56">
-        <v>1</v>
-      </c>
-      <c r="J20" s="54">
-        <v>32</v>
-      </c>
-      <c r="K20" s="52">
-        <v>14.4</v>
-      </c>
-      <c r="L20" s="52">
-        <v>3.2</v>
-      </c>
-      <c r="M20" s="52">
-        <v>4020</v>
-      </c>
-      <c r="N20" s="52">
-        <v>1170</v>
+        <v>0</v>
+      </c>
+      <c r="H20" s="48">
+        <v>1</v>
+      </c>
+      <c r="I20" s="48">
+        <v>4</v>
+      </c>
+      <c r="J20" s="47">
+        <v>23.046874999999996</v>
+      </c>
+      <c r="K20" s="48">
+        <v>15.3</v>
+      </c>
+      <c r="L20" s="48">
+        <v>5</v>
+      </c>
+      <c r="M20" s="48">
+        <v>6490</v>
+      </c>
+      <c r="N20" s="48">
+        <v>2670</v>
       </c>
       <c r="O20" s="57">
-        <v>3.44</v>
+        <v>2.4307116104868913</v>
       </c>
       <c r="P20" s="52">
         <v>0</v>
       </c>
-      <c r="Q20" s="74">
-        <v>3</v>
-      </c>
-      <c r="R20" s="48">
-        <v>1</v>
-      </c>
-      <c r="S20" s="74">
-        <v>0</v>
-      </c>
-      <c r="T20" s="73">
-        <v>0</v>
-      </c>
-      <c r="U20" s="58">
-        <v>0</v>
-      </c>
-      <c r="V20" s="153">
-        <v>3</v>
-      </c>
-      <c r="W20" s="153">
-        <v>1</v>
+      <c r="Q20" s="73">
+        <v>2</v>
+      </c>
+      <c r="R20" s="73">
+        <v>0</v>
+      </c>
+      <c r="S20" s="73">
+        <v>1</v>
+      </c>
+      <c r="T20" s="59">
+        <v>1</v>
+      </c>
+      <c r="U20" s="73">
+        <v>0</v>
+      </c>
+      <c r="V20" s="151">
+        <v>2</v>
+      </c>
+      <c r="W20" s="151">
+        <v>0</v>
       </c>
       <c r="X20" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="74">
         <v>1</v>
@@ -5177,9 +5166,11 @@
       <c r="Z20" s="48">
         <v>0</v>
       </c>
-      <c r="AA20" s="60"/>
-      <c r="AB20" s="74">
-        <v>2</v>
+      <c r="AA20" s="48">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="48">
+        <v>0</v>
       </c>
       <c r="AC20" s="48">
         <v>0</v>
@@ -5187,89 +5178,95 @@
       <c r="AD20" s="48">
         <v>0</v>
       </c>
-      <c r="AE20" s="74">
-        <v>9</v>
-      </c>
-      <c r="AF20" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="74">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="72">
+      <c r="AE20" s="48">
+        <v>21</v>
+      </c>
+      <c r="AF20" s="48">
         <v>6</v>
       </c>
-      <c r="AL20" s="74">
-        <v>1</v>
+      <c r="AG20" s="48">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="48">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="48">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="42">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="47">
+        <v>2.8</v>
+      </c>
+      <c r="AL20" s="48">
+        <v>2</v>
       </c>
       <c r="AM20" s="48">
         <v>0</v>
       </c>
       <c r="AN20" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO20" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP20" s="48">
         <v>0</v>
       </c>
-      <c r="AQ20" s="74">
-        <v>1</v>
+      <c r="AQ20" s="48">
+        <v>2</v>
       </c>
       <c r="AR20" s="42">
         <v>0</v>
       </c>
-      <c r="AS20" s="52"/>
-      <c r="AT20" s="99">
+      <c r="AS20" s="48">
+        <v>7</v>
+      </c>
+      <c r="AT20" s="65">
         <v>0</v>
       </c>
       <c r="AU20" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" s="52">
         <v>0</v>
       </c>
-      <c r="AW20" s="99">
+      <c r="AW20" s="62">
         <v>0</v>
       </c>
       <c r="AX20" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY20" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" s="47">
-        <v>1.7</v>
+        <v>60</v>
       </c>
       <c r="BA20" s="47">
-        <v>1.7</v>
-      </c>
-      <c r="BB20" s="99"/>
-      <c r="BC20" s="99"/>
-      <c r="BD20" s="99"/>
-      <c r="BE20" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="BF20" s="101">
-        <v>43027</v>
-      </c>
-      <c r="BG20" s="139">
-        <v>43079</v>
-      </c>
-      <c r="BH20" s="139">
-        <v>43079</v>
-      </c>
-      <c r="BI20" s="101"/>
-      <c r="BJ20" s="102" t="s">
-        <v>43</v>
+        <v>60</v>
+      </c>
+      <c r="BB20" s="65"/>
+      <c r="BC20" s="65"/>
+      <c r="BD20" s="65"/>
+      <c r="BE20" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF20" s="49">
+        <v>42604</v>
+      </c>
+      <c r="BG20" s="137">
+        <v>44909</v>
+      </c>
+      <c r="BH20" s="137">
+        <v>44909</v>
+      </c>
+      <c r="BI20" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ20" s="98" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
@@ -5336,10 +5333,10 @@
       <c r="U21" s="58">
         <v>0</v>
       </c>
-      <c r="V21" s="153">
-        <v>3</v>
-      </c>
-      <c r="W21" s="153">
+      <c r="V21" s="152">
+        <v>3</v>
+      </c>
+      <c r="W21" s="152">
         <v>1</v>
       </c>
       <c r="X21" s="52">
@@ -5476,10 +5473,10 @@
       <c r="U22" s="93">
         <v>0</v>
       </c>
-      <c r="V22" s="152">
-        <v>3</v>
-      </c>
-      <c r="W22" s="153">
+      <c r="V22" s="151">
+        <v>3</v>
+      </c>
+      <c r="W22" s="152">
         <v>1</v>
       </c>
       <c r="X22" s="52">
@@ -5662,10 +5659,10 @@
       <c r="U23" s="73">
         <v>0</v>
       </c>
-      <c r="V23" s="152">
-        <v>2</v>
-      </c>
-      <c r="W23" s="152">
+      <c r="V23" s="151">
+        <v>2</v>
+      </c>
+      <c r="W23" s="151">
         <v>0</v>
       </c>
       <c r="X23" s="52">
@@ -5844,10 +5841,10 @@
       <c r="U24" s="52">
         <v>0</v>
       </c>
-      <c r="V24" s="155">
-        <v>3</v>
-      </c>
-      <c r="W24" s="153">
+      <c r="V24" s="154">
+        <v>3</v>
+      </c>
+      <c r="W24" s="152">
         <v>1</v>
       </c>
       <c r="X24" s="52">
@@ -6020,10 +6017,10 @@
       <c r="U25" s="52">
         <v>0</v>
       </c>
-      <c r="V25" s="155">
+      <c r="V25" s="154">
         <v>4</v>
       </c>
-      <c r="W25" s="152">
+      <c r="W25" s="151">
         <v>2</v>
       </c>
       <c r="X25" s="52">
@@ -6204,10 +6201,10 @@
       <c r="U26" s="52">
         <v>0</v>
       </c>
-      <c r="V26" s="155">
-        <v>3</v>
-      </c>
-      <c r="W26" s="153">
+      <c r="V26" s="154">
+        <v>3</v>
+      </c>
+      <c r="W26" s="152">
         <v>1</v>
       </c>
       <c r="X26" s="52">
@@ -6388,10 +6385,10 @@
       <c r="U27" s="86">
         <v>0</v>
       </c>
-      <c r="V27" s="155">
-        <v>3</v>
-      </c>
-      <c r="W27" s="153">
+      <c r="V27" s="154">
+        <v>3</v>
+      </c>
+      <c r="W27" s="152">
         <v>1</v>
       </c>
       <c r="X27" s="86">
@@ -6566,10 +6563,10 @@
       <c r="U28" s="78">
         <v>0</v>
       </c>
-      <c r="V28" s="154">
-        <v>3</v>
-      </c>
-      <c r="W28" s="153">
+      <c r="V28" s="153">
+        <v>3</v>
+      </c>
+      <c r="W28" s="152">
         <v>1</v>
       </c>
       <c r="X28" s="52">
@@ -6748,10 +6745,10 @@
       <c r="U29" s="106">
         <v>0</v>
       </c>
-      <c r="V29" s="153">
-        <v>3</v>
-      </c>
-      <c r="W29" s="153">
+      <c r="V29" s="152">
+        <v>3</v>
+      </c>
+      <c r="W29" s="152">
         <v>1</v>
       </c>
       <c r="X29" s="39">
@@ -6922,10 +6919,10 @@
       <c r="U30" s="73">
         <v>0</v>
       </c>
-      <c r="V30" s="156">
-        <v>2</v>
-      </c>
-      <c r="W30" s="152">
+      <c r="V30" s="155">
+        <v>2</v>
+      </c>
+      <c r="W30" s="151">
         <v>0</v>
       </c>
       <c r="X30" s="52">
@@ -7104,10 +7101,10 @@
       <c r="U31" s="52">
         <v>1</v>
       </c>
-      <c r="V31" s="155">
+      <c r="V31" s="154">
         <v>4</v>
       </c>
-      <c r="W31" s="152">
+      <c r="W31" s="151">
         <v>2</v>
       </c>
       <c r="X31" s="52">
@@ -7244,10 +7241,10 @@
       <c r="U32" s="52">
         <v>0</v>
       </c>
-      <c r="V32" s="155">
+      <c r="V32" s="154">
         <v>4</v>
       </c>
-      <c r="W32" s="152">
+      <c r="W32" s="151">
         <v>2</v>
       </c>
       <c r="X32" s="52">
@@ -7386,10 +7383,10 @@
       <c r="U33" s="52">
         <v>1</v>
       </c>
-      <c r="V33" s="155">
+      <c r="V33" s="154">
         <v>4</v>
       </c>
-      <c r="W33" s="152">
+      <c r="W33" s="151">
         <v>2</v>
       </c>
       <c r="X33" s="52">
@@ -7528,10 +7525,10 @@
       <c r="U34" s="52">
         <v>0</v>
       </c>
-      <c r="V34" s="155">
-        <v>3</v>
-      </c>
-      <c r="W34" s="153">
+      <c r="V34" s="154">
+        <v>3</v>
+      </c>
+      <c r="W34" s="152">
         <v>1</v>
       </c>
       <c r="X34" s="52">
@@ -7706,10 +7703,10 @@
       <c r="U35" s="73">
         <v>0</v>
       </c>
-      <c r="V35" s="152">
-        <v>2</v>
-      </c>
-      <c r="W35" s="152">
+      <c r="V35" s="151">
+        <v>2</v>
+      </c>
+      <c r="W35" s="151">
         <v>0</v>
       </c>
       <c r="X35" s="52">
@@ -7894,10 +7891,10 @@
       <c r="U36" s="73">
         <v>0</v>
       </c>
-      <c r="V36" s="152">
-        <v>3</v>
-      </c>
-      <c r="W36" s="153">
+      <c r="V36" s="151">
+        <v>3</v>
+      </c>
+      <c r="W36" s="152">
         <v>1</v>
       </c>
       <c r="X36" s="52">
@@ -8076,10 +8073,10 @@
       <c r="U37" s="52">
         <v>1</v>
       </c>
-      <c r="V37" s="155">
+      <c r="V37" s="154">
         <v>4</v>
       </c>
-      <c r="W37" s="152">
+      <c r="W37" s="151">
         <v>2</v>
       </c>
       <c r="X37" s="52">
@@ -8218,10 +8215,10 @@
       <c r="U38" s="52">
         <v>0</v>
       </c>
-      <c r="V38" s="155">
-        <v>3</v>
-      </c>
-      <c r="W38" s="153">
+      <c r="V38" s="154">
+        <v>3</v>
+      </c>
+      <c r="W38" s="152">
         <v>1</v>
       </c>
       <c r="X38" s="52">
@@ -8394,10 +8391,10 @@
       <c r="U39" s="73">
         <v>0</v>
       </c>
-      <c r="V39" s="152">
-        <v>3</v>
-      </c>
-      <c r="W39" s="153">
+      <c r="V39" s="151">
+        <v>3</v>
+      </c>
+      <c r="W39" s="152">
         <v>1</v>
       </c>
       <c r="X39" s="52">
@@ -8576,10 +8573,10 @@
       <c r="U40" s="125">
         <v>1</v>
       </c>
-      <c r="V40" s="156">
+      <c r="V40" s="155">
         <v>4</v>
       </c>
-      <c r="W40" s="152">
+      <c r="W40" s="151">
         <v>2</v>
       </c>
       <c r="X40" s="108">
@@ -8624,7 +8621,7 @@
       <c r="AQ40" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="AR40" s="150" t="s">
+      <c r="AR40" s="149" t="s">
         <v>45</v>
       </c>
       <c r="AS40" s="107">
@@ -8730,10 +8727,10 @@
       <c r="U41" s="52">
         <v>1</v>
       </c>
-      <c r="V41" s="155">
+      <c r="V41" s="154">
         <v>4</v>
       </c>
-      <c r="W41" s="152">
+      <c r="W41" s="151">
         <v>2</v>
       </c>
       <c r="X41" s="52">
@@ -8872,10 +8869,10 @@
       <c r="U42" s="52">
         <v>1</v>
       </c>
-      <c r="V42" s="155">
+      <c r="V42" s="154">
         <v>4</v>
       </c>
-      <c r="W42" s="152">
+      <c r="W42" s="151">
         <v>2</v>
       </c>
       <c r="X42" s="52">
@@ -9056,10 +9053,10 @@
       <c r="U43" s="52">
         <v>1</v>
       </c>
-      <c r="V43" s="155">
+      <c r="V43" s="154">
         <v>4</v>
       </c>
-      <c r="W43" s="152">
+      <c r="W43" s="151">
         <v>2</v>
       </c>
       <c r="X43" s="52">
@@ -9198,10 +9195,10 @@
       <c r="U44" s="78">
         <v>0</v>
       </c>
-      <c r="V44" s="154">
+      <c r="V44" s="153">
         <v>4</v>
       </c>
-      <c r="W44" s="152">
+      <c r="W44" s="151">
         <v>2</v>
       </c>
       <c r="X44" s="52">
@@ -9338,10 +9335,10 @@
       <c r="U45" s="52">
         <v>1</v>
       </c>
-      <c r="V45" s="155">
+      <c r="V45" s="154">
         <v>4</v>
       </c>
-      <c r="W45" s="152">
+      <c r="W45" s="151">
         <v>2</v>
       </c>
       <c r="X45" s="52">
@@ -9478,10 +9475,10 @@
       <c r="U46" s="52">
         <v>0</v>
       </c>
-      <c r="V46" s="155">
+      <c r="V46" s="154">
         <v>4</v>
       </c>
-      <c r="W46" s="152">
+      <c r="W46" s="151">
         <v>2</v>
       </c>
       <c r="X46" s="52">
@@ -9620,10 +9617,10 @@
       <c r="U47" s="73">
         <v>0</v>
       </c>
-      <c r="V47" s="152">
+      <c r="V47" s="151">
         <v>4</v>
       </c>
-      <c r="W47" s="152">
+      <c r="W47" s="151">
         <v>2</v>
       </c>
       <c r="X47" s="52">
@@ -9802,10 +9799,10 @@
       <c r="U48" s="52">
         <v>0</v>
       </c>
-      <c r="V48" s="155">
-        <v>3</v>
-      </c>
-      <c r="W48" s="153">
+      <c r="V48" s="154">
+        <v>3</v>
+      </c>
+      <c r="W48" s="152">
         <v>1</v>
       </c>
       <c r="X48" s="52">
@@ -9942,10 +9939,10 @@
       <c r="U49" s="58">
         <v>0</v>
       </c>
-      <c r="V49" s="153">
+      <c r="V49" s="152">
         <v>4</v>
       </c>
-      <c r="W49" s="152">
+      <c r="W49" s="151">
         <v>2</v>
       </c>
       <c r="X49" s="52">
@@ -10124,10 +10121,10 @@
       <c r="U50" s="52">
         <v>0</v>
       </c>
-      <c r="V50" s="155">
-        <v>3</v>
-      </c>
-      <c r="W50" s="153">
+      <c r="V50" s="154">
+        <v>3</v>
+      </c>
+      <c r="W50" s="152">
         <v>1</v>
       </c>
       <c r="X50" s="52">
@@ -10308,10 +10305,10 @@
       <c r="U51" s="52">
         <v>0</v>
       </c>
-      <c r="V51" s="155">
+      <c r="V51" s="154">
         <v>4</v>
       </c>
-      <c r="W51" s="152">
+      <c r="W51" s="151">
         <v>2</v>
       </c>
       <c r="X51" s="52">
@@ -10448,10 +10445,10 @@
       <c r="U52" s="52">
         <v>1</v>
       </c>
-      <c r="V52" s="155">
+      <c r="V52" s="154">
         <v>4</v>
       </c>
-      <c r="W52" s="152">
+      <c r="W52" s="151">
         <v>2</v>
       </c>
       <c r="X52" s="52">
@@ -10588,10 +10585,10 @@
       <c r="U53" s="52">
         <v>0</v>
       </c>
-      <c r="V53" s="155">
-        <v>3</v>
-      </c>
-      <c r="W53" s="153">
+      <c r="V53" s="154">
+        <v>3</v>
+      </c>
+      <c r="W53" s="152">
         <v>1</v>
       </c>
       <c r="X53" s="52">
@@ -10730,10 +10727,10 @@
       <c r="U54" s="48">
         <v>0</v>
       </c>
-      <c r="V54" s="152">
-        <v>3</v>
-      </c>
-      <c r="W54" s="153">
+      <c r="V54" s="151">
+        <v>3</v>
+      </c>
+      <c r="W54" s="152">
         <v>1</v>
       </c>
       <c r="X54" s="52">
@@ -10910,10 +10907,10 @@
       <c r="U55" s="86">
         <v>1</v>
       </c>
-      <c r="V55" s="155">
+      <c r="V55" s="154">
         <v>4</v>
       </c>
-      <c r="W55" s="152">
+      <c r="W55" s="151">
         <v>2</v>
       </c>
       <c r="X55" s="86">
@@ -11054,10 +11051,10 @@
       <c r="U56" s="52">
         <v>0</v>
       </c>
-      <c r="V56" s="155">
-        <v>3</v>
-      </c>
-      <c r="W56" s="153">
+      <c r="V56" s="154">
+        <v>3</v>
+      </c>
+      <c r="W56" s="152">
         <v>1</v>
       </c>
       <c r="X56" s="52">
@@ -11242,10 +11239,10 @@
       <c r="U57" s="35">
         <v>0</v>
       </c>
-      <c r="V57" s="152">
+      <c r="V57" s="151">
         <v>4</v>
       </c>
-      <c r="W57" s="152">
+      <c r="W57" s="151">
         <v>2</v>
       </c>
       <c r="X57" s="39">
@@ -11424,10 +11421,10 @@
       <c r="U58" s="52">
         <v>0</v>
       </c>
-      <c r="V58" s="155">
-        <v>3</v>
-      </c>
-      <c r="W58" s="153">
+      <c r="V58" s="154">
+        <v>3</v>
+      </c>
+      <c r="W58" s="152">
         <v>1</v>
       </c>
       <c r="X58" s="52">
@@ -11542,19 +11539,19 @@
     </row>
     <row r="59" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="48">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>146</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E59" s="72">
-        <v>43.836111111111109</v>
+        <v>58.388888888888886</v>
       </c>
       <c r="F59" s="75">
         <v>0</v>
@@ -11569,31 +11566,29 @@
         <v>4</v>
       </c>
       <c r="J59" s="47">
-        <v>25.344352617079892</v>
+        <v>23.422090729783037</v>
       </c>
       <c r="K59" s="48">
-        <v>12.1</v>
-      </c>
-      <c r="L59" s="48">
-        <v>4.4000000000000004</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L59" s="52"/>
       <c r="M59" s="48">
-        <v>5160</v>
+        <v>3120</v>
       </c>
       <c r="N59" s="48">
-        <v>1570</v>
+        <v>1360</v>
       </c>
       <c r="O59" s="57">
-        <v>3.2866242038216562</v>
+        <v>2.2941176470588234</v>
       </c>
       <c r="P59" s="52">
         <v>0</v>
       </c>
       <c r="Q59" s="73">
-        <v>2</v>
-      </c>
-      <c r="R59" s="73">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="R59" s="48">
+        <v>1</v>
       </c>
       <c r="S59" s="73">
         <v>0</v>
@@ -11604,10 +11599,10 @@
       <c r="U59" s="73">
         <v>0</v>
       </c>
-      <c r="V59" s="152">
-        <v>1</v>
-      </c>
-      <c r="W59" s="152">
+      <c r="V59" s="155">
+        <v>2</v>
+      </c>
+      <c r="W59" s="151">
         <v>0</v>
       </c>
       <c r="X59" s="52">
@@ -11626,13 +11621,13 @@
         <v>1</v>
       </c>
       <c r="AC59" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="48">
         <v>0</v>
       </c>
       <c r="AE59" s="48">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF59" s="48">
         <v>0</v>
@@ -11646,11 +11641,11 @@
       <c r="AI59" s="48">
         <v>0</v>
       </c>
-      <c r="AJ59" s="59">
-        <v>1</v>
+      <c r="AJ59" s="52">
+        <v>0</v>
       </c>
       <c r="AK59" s="47">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AL59" s="48">
         <v>3</v>
@@ -11674,13 +11669,13 @@
         <v>0</v>
       </c>
       <c r="AS59" s="48">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AT59" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV59" s="52">
         <v>1</v>
@@ -11695,34 +11690,34 @@
         <v>1</v>
       </c>
       <c r="AZ59" s="47">
-        <v>10.366666666666667</v>
+        <v>25.266666666666666</v>
       </c>
       <c r="BA59" s="47">
-        <v>12.866666666666667</v>
+        <v>33.633333333333333</v>
       </c>
       <c r="BB59" s="65">
         <v>0</v>
       </c>
       <c r="BC59" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD59" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE59" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF59" s="49">
-        <v>42144</v>
+        <v>41786</v>
       </c>
       <c r="BG59" s="134" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="BH59" s="134">
-        <v>42537</v>
+        <v>42810</v>
       </c>
       <c r="BI59" s="53" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="BJ59" s="98" t="s">
         <v>43</v>
@@ -11730,259 +11725,255 @@
     </row>
     <row r="60" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="48">
+        <v>61</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="72">
+        <v>65.836111111111109</v>
+      </c>
+      <c r="F60" s="55">
+        <v>1</v>
+      </c>
+      <c r="G60" s="52">
+        <v>1</v>
+      </c>
+      <c r="H60" s="48">
+        <v>1</v>
+      </c>
+      <c r="I60" s="48">
+        <v>5</v>
+      </c>
+      <c r="J60" s="47">
+        <v>19.607156612163443</v>
+      </c>
+      <c r="K60" s="48">
+        <v>10.3</v>
+      </c>
+      <c r="L60" s="48">
+        <v>3.9</v>
+      </c>
+      <c r="M60" s="48">
+        <v>4110</v>
+      </c>
+      <c r="N60" s="48">
+        <v>2370</v>
+      </c>
+      <c r="O60" s="57">
+        <v>1.7341772151898733</v>
+      </c>
+      <c r="P60" s="52">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="73">
+        <v>2</v>
+      </c>
+      <c r="R60" s="73">
+        <v>0</v>
+      </c>
+      <c r="S60" s="73">
+        <v>1</v>
+      </c>
+      <c r="T60" s="59">
+        <v>1</v>
+      </c>
+      <c r="U60" s="73">
+        <v>0</v>
+      </c>
+      <c r="V60" s="151">
+        <v>2</v>
+      </c>
+      <c r="W60" s="151">
+        <v>0</v>
+      </c>
+      <c r="X60" s="52">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="48">
+        <v>2</v>
+      </c>
+      <c r="AB60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="48">
+        <v>28</v>
+      </c>
+      <c r="AF60" s="48">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="48">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="48">
+        <v>1</v>
+      </c>
+      <c r="AI60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="47">
+        <v>11</v>
+      </c>
+      <c r="AL60" s="48">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="48">
+        <v>1</v>
+      </c>
+      <c r="AN60" s="48">
+        <v>2</v>
+      </c>
+      <c r="AO60" s="48">
+        <v>1</v>
+      </c>
+      <c r="AP60" s="48">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="48">
+        <v>3</v>
+      </c>
+      <c r="AR60" s="76">
+        <v>1</v>
+      </c>
+      <c r="AS60" s="48">
+        <v>7</v>
+      </c>
+      <c r="AT60" s="65">
+        <v>0</v>
+      </c>
+      <c r="AU60" s="52">
+        <v>1</v>
+      </c>
+      <c r="AV60" s="52">
+        <v>0</v>
+      </c>
+      <c r="AW60" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX60" s="62">
+        <v>0</v>
+      </c>
+      <c r="AY60" s="65">
+        <v>0</v>
+      </c>
+      <c r="AZ60" s="47">
         <v>60</v>
       </c>
-      <c r="B60" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="E60" s="72">
-        <v>58.388888888888886</v>
-      </c>
-      <c r="F60" s="75">
-        <v>0</v>
-      </c>
-      <c r="G60" s="52">
-        <v>0</v>
-      </c>
-      <c r="H60" s="48">
-        <v>0</v>
-      </c>
-      <c r="I60" s="48">
-        <v>4</v>
-      </c>
-      <c r="J60" s="47">
-        <v>23.422090729783037</v>
-      </c>
-      <c r="K60" s="48">
-        <v>12</v>
-      </c>
-      <c r="L60" s="52"/>
-      <c r="M60" s="48">
-        <v>3120</v>
-      </c>
-      <c r="N60" s="48">
-        <v>1360</v>
-      </c>
-      <c r="O60" s="57">
-        <v>2.2941176470588234</v>
-      </c>
-      <c r="P60" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="73">
-        <v>3</v>
-      </c>
-      <c r="R60" s="48">
-        <v>1</v>
-      </c>
-      <c r="S60" s="73">
-        <v>0</v>
-      </c>
-      <c r="T60" s="73">
-        <v>0</v>
-      </c>
-      <c r="U60" s="73">
-        <v>0</v>
-      </c>
-      <c r="V60" s="156">
-        <v>2</v>
-      </c>
-      <c r="W60" s="152">
-        <v>0</v>
-      </c>
-      <c r="X60" s="52">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="74">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB60" s="48">
-        <v>1</v>
-      </c>
-      <c r="AC60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="48">
-        <v>44</v>
-      </c>
-      <c r="AF60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="52">
-        <v>0</v>
-      </c>
-      <c r="AK60" s="47">
-        <v>10.5</v>
-      </c>
-      <c r="AL60" s="48">
-        <v>3</v>
-      </c>
-      <c r="AM60" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AP60" s="48">
-        <v>0</v>
-      </c>
-      <c r="AQ60" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR60" s="59">
-        <v>0</v>
-      </c>
-      <c r="AS60" s="48">
-        <v>18</v>
-      </c>
-      <c r="AT60" s="65">
-        <v>1</v>
-      </c>
-      <c r="AU60" s="52">
-        <v>1</v>
-      </c>
-      <c r="AV60" s="52">
-        <v>1</v>
-      </c>
-      <c r="AW60" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX60" s="65">
-        <v>1</v>
-      </c>
-      <c r="AY60" s="65">
-        <v>1</v>
-      </c>
-      <c r="AZ60" s="47">
-        <v>25.266666666666666</v>
-      </c>
       <c r="BA60" s="47">
-        <v>33.633333333333333</v>
-      </c>
-      <c r="BB60" s="65">
-        <v>0</v>
-      </c>
-      <c r="BC60" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD60" s="65">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="BB60" s="65"/>
+      <c r="BC60" s="65"/>
+      <c r="BD60" s="65"/>
       <c r="BE60" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF60" s="49">
-        <v>41786</v>
-      </c>
-      <c r="BG60" s="134" t="s">
-        <v>42</v>
-      </c>
-      <c r="BH60" s="134">
-        <v>42810</v>
+        <v>41822</v>
+      </c>
+      <c r="BG60" s="137">
+        <v>44559</v>
+      </c>
+      <c r="BH60" s="137">
+        <v>44559</v>
       </c>
       <c r="BI60" s="53" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BJ60" s="98" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="48">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E61" s="72">
-        <v>70.347222222222229</v>
-      </c>
-      <c r="F61" s="55">
-        <v>1</v>
+        <v>60.18611111111111</v>
+      </c>
+      <c r="F61" s="75">
+        <v>0</v>
       </c>
       <c r="G61" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="48">
         <v>0</v>
       </c>
       <c r="I61" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" s="47">
-        <v>19.100091827364558</v>
+        <v>22.67573696145125</v>
       </c>
       <c r="K61" s="48">
-        <v>9</v>
+        <v>13.7</v>
       </c>
       <c r="L61" s="48">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="M61" s="48">
-        <v>4900</v>
+        <v>6220</v>
       </c>
       <c r="N61" s="48">
-        <v>2280</v>
+        <v>3300</v>
       </c>
       <c r="O61" s="57">
-        <v>2.1491228070175437</v>
+        <v>1.8848484848484848</v>
       </c>
       <c r="P61" s="52">
         <v>0</v>
       </c>
       <c r="Q61" s="73">
-        <v>2</v>
-      </c>
-      <c r="R61" s="73">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="R61" s="48">
+        <v>1</v>
       </c>
       <c r="S61" s="73">
-        <v>0</v>
-      </c>
-      <c r="T61" s="73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T61" s="59">
+        <v>1</v>
       </c>
       <c r="U61" s="73">
         <v>0</v>
       </c>
-      <c r="V61" s="152">
-        <v>1</v>
+      <c r="V61" s="151">
+        <v>3</v>
       </c>
       <c r="W61" s="152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="52">
         <v>0</v>
@@ -11997,34 +11988,34 @@
         <v>2</v>
       </c>
       <c r="AB61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE61" s="48">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AF61" s="48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG61" s="48">
         <v>1</v>
       </c>
       <c r="AH61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ61" s="59">
         <v>1</v>
       </c>
       <c r="AK61" s="47">
-        <v>8.6999999999999993</v>
+        <v>10.5</v>
       </c>
       <c r="AL61" s="48">
         <v>3</v>
@@ -12033,64 +12024,70 @@
         <v>1</v>
       </c>
       <c r="AN61" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO61" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP61" s="48">
         <v>0</v>
       </c>
       <c r="AQ61" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR61" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR61" s="76">
+        <v>1</v>
       </c>
       <c r="AS61" s="48">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AT61" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" s="52">
         <v>1</v>
       </c>
       <c r="AV61" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW61" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX61" s="62">
+        <v>1</v>
+      </c>
+      <c r="AW61" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX61" s="65">
         <v>1</v>
       </c>
       <c r="AY61" s="65">
         <v>1</v>
       </c>
       <c r="AZ61" s="47">
-        <v>35.799999999999997</v>
+        <v>21.133333333333333</v>
       </c>
       <c r="BA61" s="47">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="BB61" s="65"/>
-      <c r="BC61" s="65"/>
-      <c r="BD61" s="65"/>
+        <v>22.3</v>
+      </c>
+      <c r="BB61" s="65">
+        <v>1</v>
+      </c>
+      <c r="BC61" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD61" s="65">
+        <v>0</v>
+      </c>
       <c r="BE61" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF61" s="49">
-        <v>41907</v>
-      </c>
-      <c r="BG61" s="134">
-        <v>42997</v>
+        <v>41857</v>
+      </c>
+      <c r="BG61" s="134" t="s">
+        <v>48</v>
       </c>
       <c r="BH61" s="134">
-        <v>42997</v>
+        <v>42536</v>
       </c>
       <c r="BI61" s="53" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="BJ61" s="98" t="s">
         <v>43</v>
@@ -12098,22 +12095,22 @@
     </row>
     <row r="62" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="48">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E62" s="72">
-        <v>52.538888888888891</v>
-      </c>
-      <c r="F62" s="75">
-        <v>0</v>
+        <v>70.347222222222229</v>
+      </c>
+      <c r="F62" s="55">
+        <v>1</v>
       </c>
       <c r="G62" s="52">
         <v>1</v>
@@ -12125,22 +12122,22 @@
         <v>5</v>
       </c>
       <c r="J62" s="47">
-        <v>22.4058769513315</v>
+        <v>19.100091827364558</v>
       </c>
       <c r="K62" s="48">
-        <v>15.4</v>
+        <v>9</v>
       </c>
       <c r="L62" s="48">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="M62" s="48">
-        <v>2990</v>
+        <v>4900</v>
       </c>
       <c r="N62" s="48">
-        <v>1980</v>
+        <v>2280</v>
       </c>
       <c r="O62" s="57">
-        <v>1.5101010101010102</v>
+        <v>2.1491228070175437</v>
       </c>
       <c r="P62" s="52">
         <v>0</v>
@@ -12152,18 +12149,18 @@
         <v>0</v>
       </c>
       <c r="S62" s="73">
-        <v>1</v>
-      </c>
-      <c r="T62" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T62" s="73">
+        <v>0</v>
       </c>
       <c r="U62" s="73">
         <v>0</v>
       </c>
-      <c r="V62" s="152">
-        <v>2</v>
-      </c>
-      <c r="W62" s="152">
+      <c r="V62" s="151">
+        <v>1</v>
+      </c>
+      <c r="W62" s="151">
         <v>0</v>
       </c>
       <c r="X62" s="52">
@@ -12188,25 +12185,25 @@
         <v>0</v>
       </c>
       <c r="AE62" s="48">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AF62" s="48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG62" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH62" s="48">
         <v>0</v>
       </c>
       <c r="AI62" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ62" s="59">
         <v>1</v>
       </c>
       <c r="AK62" s="47">
-        <v>6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AL62" s="48">
         <v>3</v>
@@ -12215,24 +12212,24 @@
         <v>1</v>
       </c>
       <c r="AN62" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO62" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP62" s="48">
         <v>0</v>
       </c>
       <c r="AQ62" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR62" s="76">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR62" s="59">
+        <v>0</v>
       </c>
       <c r="AS62" s="48">
-        <v>7</v>
-      </c>
-      <c r="AT62" s="62">
+        <v>5</v>
+      </c>
+      <c r="AT62" s="65">
         <v>0</v>
       </c>
       <c r="AU62" s="52">
@@ -12245,16 +12242,16 @@
         <v>0</v>
       </c>
       <c r="AX62" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY62" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ62" s="47">
-        <v>60</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="BA62" s="47">
-        <v>60</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="BB62" s="65"/>
       <c r="BC62" s="65"/>
@@ -12263,162 +12260,162 @@
         <v>41</v>
       </c>
       <c r="BF62" s="49">
-        <v>41935</v>
-      </c>
-      <c r="BG62" s="137">
-        <v>45215</v>
-      </c>
-      <c r="BH62" s="137">
-        <v>45215</v>
+        <v>41907</v>
+      </c>
+      <c r="BG62" s="134">
+        <v>42997</v>
+      </c>
+      <c r="BH62" s="134">
+        <v>42997</v>
       </c>
       <c r="BI62" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ62" s="98" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="48">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B63" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D63" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" s="72">
+        <v>52.538888888888891</v>
+      </c>
+      <c r="F63" s="75">
+        <v>0</v>
+      </c>
+      <c r="G63" s="52">
+        <v>1</v>
+      </c>
+      <c r="H63" s="48">
+        <v>0</v>
+      </c>
+      <c r="I63" s="48">
+        <v>5</v>
+      </c>
+      <c r="J63" s="47">
+        <v>22.4058769513315</v>
+      </c>
+      <c r="K63" s="48">
+        <v>15.4</v>
+      </c>
+      <c r="L63" s="48">
+        <v>4.5</v>
+      </c>
+      <c r="M63" s="48">
+        <v>2990</v>
+      </c>
+      <c r="N63" s="48">
+        <v>1980</v>
+      </c>
+      <c r="O63" s="57">
+        <v>1.5101010101010102</v>
+      </c>
+      <c r="P63" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="73">
+        <v>2</v>
+      </c>
+      <c r="R63" s="73">
+        <v>0</v>
+      </c>
+      <c r="S63" s="73">
+        <v>1</v>
+      </c>
+      <c r="T63" s="59">
+        <v>1</v>
+      </c>
+      <c r="U63" s="73">
+        <v>0</v>
+      </c>
+      <c r="V63" s="151">
+        <v>2</v>
+      </c>
+      <c r="W63" s="151">
+        <v>0</v>
+      </c>
+      <c r="X63" s="52">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="48">
+        <v>2</v>
+      </c>
+      <c r="AB63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="48">
+        <v>45</v>
+      </c>
+      <c r="AF63" s="48">
+        <v>3</v>
+      </c>
+      <c r="AG63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="48">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="48">
+        <v>1</v>
+      </c>
+      <c r="AJ63" s="59">
+        <v>1</v>
+      </c>
+      <c r="AK63" s="47">
         <v>6</v>
       </c>
-      <c r="C63" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="E63" s="72">
-        <v>55.694444444444443</v>
-      </c>
-      <c r="F63" s="75">
-        <v>0</v>
-      </c>
-      <c r="G63" s="52">
-        <v>1</v>
-      </c>
-      <c r="H63" s="48">
-        <v>0</v>
-      </c>
-      <c r="I63" s="48">
-        <v>4</v>
-      </c>
-      <c r="J63" s="47">
-        <v>25.282569898869724</v>
-      </c>
-      <c r="K63" s="48">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="L63" s="48">
-        <v>4.7</v>
-      </c>
-      <c r="M63" s="48">
-        <v>4770</v>
-      </c>
-      <c r="N63" s="48">
-        <v>2110</v>
-      </c>
-      <c r="O63" s="57">
-        <v>2.2606635071090047</v>
-      </c>
-      <c r="P63" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="73">
-        <v>1</v>
-      </c>
-      <c r="R63" s="73">
-        <v>0</v>
-      </c>
-      <c r="S63" s="73">
-        <v>0</v>
-      </c>
-      <c r="T63" s="73">
-        <v>0</v>
-      </c>
-      <c r="U63" s="73">
-        <v>0</v>
-      </c>
-      <c r="V63" s="152">
-        <v>1</v>
-      </c>
-      <c r="W63" s="152">
-        <v>0</v>
-      </c>
-      <c r="X63" s="52">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="74">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="48">
-        <v>25</v>
-      </c>
-      <c r="AF63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AG63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AI63" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ63" s="52">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="47">
-        <v>2.5</v>
-      </c>
-      <c r="AL63" s="74">
-        <v>1</v>
+      <c r="AL63" s="48">
+        <v>3</v>
       </c>
       <c r="AM63" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN63" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO63" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP63" s="48">
         <v>0</v>
       </c>
       <c r="AQ63" s="48">
-        <v>1</v>
-      </c>
-      <c r="AR63" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR63" s="76">
+        <v>1</v>
       </c>
       <c r="AS63" s="48">
-        <v>5</v>
-      </c>
-      <c r="AT63" s="65">
+        <v>7</v>
+      </c>
+      <c r="AT63" s="62">
         <v>0</v>
       </c>
       <c r="AU63" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" s="52">
         <v>0</v>
@@ -12445,36 +12442,36 @@
         <v>41</v>
       </c>
       <c r="BF63" s="49">
-        <v>41976</v>
-      </c>
-      <c r="BG63" s="134">
-        <v>43812</v>
-      </c>
-      <c r="BH63" s="134">
-        <v>43812</v>
+        <v>41935</v>
+      </c>
+      <c r="BG63" s="137">
+        <v>45215</v>
+      </c>
+      <c r="BH63" s="137">
+        <v>45215</v>
       </c>
       <c r="BI63" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ63" s="98" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="48">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E64" s="72">
-        <v>82.63055555555556</v>
+        <v>75.894444444444446</v>
       </c>
       <c r="F64" s="55">
         <v>1</v>
@@ -12483,37 +12480,37 @@
         <v>1</v>
       </c>
       <c r="H64" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" s="47">
-        <v>17.846519928613922</v>
+        <v>22.546576480360741</v>
       </c>
       <c r="K64" s="48">
-        <v>7.9</v>
+        <v>11.2</v>
       </c>
       <c r="L64" s="48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="M64" s="48">
-        <v>3240</v>
+        <v>6380</v>
       </c>
       <c r="N64" s="48">
-        <v>1290</v>
+        <v>1670</v>
       </c>
       <c r="O64" s="57">
-        <v>2.5116279069767442</v>
+        <v>3.8203592814371259</v>
       </c>
       <c r="P64" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="73">
-        <v>2</v>
-      </c>
-      <c r="R64" s="73">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="R64" s="48">
+        <v>1</v>
       </c>
       <c r="S64" s="73">
         <v>1</v>
@@ -12524,11 +12521,11 @@
       <c r="U64" s="111">
         <v>0</v>
       </c>
-      <c r="V64" s="152">
-        <v>2</v>
+      <c r="V64" s="151">
+        <v>3</v>
       </c>
       <c r="W64" s="152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" s="86">
         <v>0</v>
@@ -12540,41 +12537,41 @@
         <v>0</v>
       </c>
       <c r="AA64" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB64" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC64" s="48">
         <v>0</v>
       </c>
       <c r="AD64" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE64" s="48">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AF64" s="48">
+        <v>6</v>
+      </c>
+      <c r="AG64" s="48">
+        <v>1</v>
+      </c>
+      <c r="AH64" s="48">
+        <v>1</v>
+      </c>
+      <c r="AI64" s="48">
+        <v>1</v>
+      </c>
+      <c r="AJ64" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="47">
+        <v>13</v>
+      </c>
+      <c r="AL64" s="48">
         <v>4</v>
       </c>
-      <c r="AG64" s="48">
-        <v>0</v>
-      </c>
-      <c r="AH64" s="48">
-        <v>0</v>
-      </c>
-      <c r="AI64" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="52">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="47">
-        <v>5.5</v>
-      </c>
-      <c r="AL64" s="48">
-        <v>3</v>
-      </c>
       <c r="AM64" s="48">
         <v>1</v>
       </c>
@@ -12594,16 +12591,16 @@
         <v>1</v>
       </c>
       <c r="AS64" s="48">
-        <v>6</v>
-      </c>
-      <c r="AT64" s="65">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="AT64" s="62">
+        <v>1</v>
       </c>
       <c r="AU64" s="52">
         <v>0</v>
       </c>
       <c r="AV64" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW64" s="65">
         <v>1</v>
@@ -12615,34 +12612,34 @@
         <v>1</v>
       </c>
       <c r="AZ64" s="47">
-        <v>10.166666666666666</v>
+        <v>16.733333333333334</v>
       </c>
       <c r="BA64" s="47">
-        <v>10.533333333333333</v>
+        <v>21.966666666666665</v>
       </c>
       <c r="BB64" s="65">
         <v>1</v>
       </c>
       <c r="BC64" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD64" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE64" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF64" s="49">
-        <v>41970</v>
+        <v>41879</v>
       </c>
       <c r="BG64" s="134" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="BH64" s="134">
-        <v>42290</v>
+        <v>42548</v>
       </c>
       <c r="BI64" s="53" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="BJ64" s="98" t="s">
         <v>43</v>
@@ -12650,138 +12647,140 @@
     </row>
     <row r="65" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="48">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B65" s="48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C65" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D65" s="48" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E65" s="72">
-        <v>40.391666666666666</v>
+        <v>55.694444444444443</v>
       </c>
       <c r="F65" s="75">
         <v>0</v>
       </c>
       <c r="G65" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="48">
         <v>0</v>
       </c>
       <c r="I65" s="48">
+        <v>4</v>
+      </c>
+      <c r="J65" s="47">
+        <v>25.282569898869724</v>
+      </c>
+      <c r="K65" s="48">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="L65" s="48">
+        <v>4.7</v>
+      </c>
+      <c r="M65" s="48">
+        <v>4770</v>
+      </c>
+      <c r="N65" s="48">
+        <v>2110</v>
+      </c>
+      <c r="O65" s="57">
+        <v>2.2606635071090047</v>
+      </c>
+      <c r="P65" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="73">
+        <v>1</v>
+      </c>
+      <c r="R65" s="73">
+        <v>0</v>
+      </c>
+      <c r="S65" s="73">
+        <v>0</v>
+      </c>
+      <c r="T65" s="73">
+        <v>0</v>
+      </c>
+      <c r="U65" s="73">
+        <v>0</v>
+      </c>
+      <c r="V65" s="151">
+        <v>1</v>
+      </c>
+      <c r="W65" s="151">
+        <v>0</v>
+      </c>
+      <c r="X65" s="52">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="48">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="48">
+        <v>25</v>
+      </c>
+      <c r="AF65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="AL65" s="74">
+        <v>1</v>
+      </c>
+      <c r="AM65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="48">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="48">
+        <v>1</v>
+      </c>
+      <c r="AR65" s="59">
+        <v>0</v>
+      </c>
+      <c r="AS65" s="48">
         <v>5</v>
       </c>
-      <c r="J65" s="47">
-        <v>29.068773297766839</v>
-      </c>
-      <c r="K65" s="48">
-        <v>15.5</v>
-      </c>
-      <c r="L65" s="52"/>
-      <c r="M65" s="48">
-        <v>4940</v>
-      </c>
-      <c r="N65" s="48">
-        <v>1510</v>
-      </c>
-      <c r="O65" s="57">
-        <v>3.2715231788079469</v>
-      </c>
-      <c r="P65" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="48">
-        <v>4</v>
-      </c>
-      <c r="R65" s="48">
-        <v>1</v>
-      </c>
-      <c r="S65" s="73">
-        <v>0</v>
-      </c>
-      <c r="T65" s="73">
-        <v>0</v>
-      </c>
-      <c r="U65" s="73">
-        <v>0</v>
-      </c>
-      <c r="V65" s="156">
-        <v>2</v>
-      </c>
-      <c r="W65" s="152">
-        <v>0</v>
-      </c>
-      <c r="X65" s="52">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="74">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="48">
-        <v>2</v>
-      </c>
-      <c r="AB65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE65" s="48">
-        <v>46</v>
-      </c>
-      <c r="AF65" s="48">
-        <v>1</v>
-      </c>
-      <c r="AG65" s="48">
-        <v>1</v>
-      </c>
-      <c r="AH65" s="48">
-        <v>1</v>
-      </c>
-      <c r="AI65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ65" s="52">
-        <v>0</v>
-      </c>
-      <c r="AK65" s="47">
-        <v>7.7</v>
-      </c>
-      <c r="AL65" s="48">
-        <v>3</v>
-      </c>
-      <c r="AM65" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN65" s="52">
-        <v>1</v>
-      </c>
-      <c r="AO65" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP65" s="48">
-        <v>0</v>
-      </c>
-      <c r="AQ65" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR65" s="59">
-        <v>0</v>
-      </c>
-      <c r="AS65" s="48">
-        <v>6</v>
-      </c>
       <c r="AT65" s="65">
         <v>0</v>
       </c>
@@ -12797,14 +12796,14 @@
       <c r="AX65" s="62">
         <v>0</v>
       </c>
-      <c r="AY65" s="62">
+      <c r="AY65" s="65">
         <v>0</v>
       </c>
       <c r="AZ65" s="47">
-        <v>2.4666666666666668</v>
+        <v>60</v>
       </c>
       <c r="BA65" s="47">
-        <v>2.4666666666666668</v>
+        <v>60</v>
       </c>
       <c r="BB65" s="65"/>
       <c r="BC65" s="65"/>
@@ -12813,69 +12812,69 @@
         <v>41</v>
       </c>
       <c r="BF65" s="49">
-        <v>41984</v>
-      </c>
-      <c r="BG65" s="135">
-        <v>42060</v>
-      </c>
-      <c r="BH65" s="135">
-        <v>42060</v>
+        <v>41976</v>
+      </c>
+      <c r="BG65" s="134">
+        <v>43812</v>
+      </c>
+      <c r="BH65" s="134">
+        <v>43812</v>
       </c>
       <c r="BI65" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ65" s="98" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="48">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B66" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C66" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D66" s="48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E66" s="72">
-        <v>76.836111111111109</v>
+        <v>82.63055555555556</v>
       </c>
       <c r="F66" s="55">
         <v>1</v>
       </c>
       <c r="G66" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="48">
         <v>5</v>
       </c>
       <c r="J66" s="47">
-        <v>21.333333333333332</v>
+        <v>17.846519928613922</v>
       </c>
       <c r="K66" s="48">
-        <v>13.5</v>
+        <v>7.9</v>
       </c>
       <c r="L66" s="48">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="M66" s="48">
-        <v>4800</v>
+        <v>3240</v>
       </c>
       <c r="N66" s="48">
-        <v>1600</v>
+        <v>1290</v>
       </c>
       <c r="O66" s="57">
-        <v>3</v>
+        <v>2.5116279069767442</v>
       </c>
       <c r="P66" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="73">
         <v>2</v>
@@ -12892,10 +12891,10 @@
       <c r="U66" s="73">
         <v>0</v>
       </c>
-      <c r="V66" s="152">
-        <v>2</v>
-      </c>
-      <c r="W66" s="152">
+      <c r="V66" s="151">
+        <v>2</v>
+      </c>
+      <c r="W66" s="151">
         <v>0</v>
       </c>
       <c r="X66" s="52">
@@ -12908,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="AA66" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB66" s="48">
         <v>0</v>
@@ -12920,25 +12919,25 @@
         <v>0</v>
       </c>
       <c r="AE66" s="48">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="AF66" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG66" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH66" s="48">
         <v>0</v>
       </c>
       <c r="AI66" s="48">
-        <v>1</v>
-      </c>
-      <c r="AJ66" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="52">
+        <v>0</v>
       </c>
       <c r="AK66" s="47">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AL66" s="48">
         <v>3</v>
@@ -12962,16 +12961,16 @@
         <v>1</v>
       </c>
       <c r="AS66" s="48">
-        <v>20</v>
-      </c>
-      <c r="AT66" s="62">
+        <v>6</v>
+      </c>
+      <c r="AT66" s="65">
         <v>0</v>
       </c>
       <c r="AU66" s="52">
         <v>0</v>
       </c>
       <c r="AV66" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW66" s="65">
         <v>1</v>
@@ -12983,13 +12982,13 @@
         <v>1</v>
       </c>
       <c r="AZ66" s="47">
-        <v>11.166666666666666</v>
+        <v>10.166666666666666</v>
       </c>
       <c r="BA66" s="47">
-        <v>30.666666666666668</v>
+        <v>10.533333333333333</v>
       </c>
       <c r="BB66" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC66" s="65">
         <v>0</v>
@@ -13001,16 +13000,16 @@
         <v>41</v>
       </c>
       <c r="BF66" s="49">
-        <v>41990</v>
+        <v>41970</v>
       </c>
       <c r="BG66" s="134" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="BH66" s="134">
-        <v>42923</v>
+        <v>42290</v>
       </c>
       <c r="BI66" s="53" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="BJ66" s="98" t="s">
         <v>43</v>
@@ -13018,19 +13017,19 @@
     </row>
     <row r="67" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="48">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C67" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E67" s="72">
-        <v>53.802777777777777</v>
+        <v>40.391666666666666</v>
       </c>
       <c r="F67" s="75">
         <v>0</v>
@@ -13045,31 +13044,29 @@
         <v>5</v>
       </c>
       <c r="J67" s="47">
-        <v>35.055631763450684</v>
+        <v>29.068773297766839</v>
       </c>
       <c r="K67" s="48">
-        <v>11.7</v>
-      </c>
-      <c r="L67" s="48">
-        <v>4.3</v>
-      </c>
+        <v>15.5</v>
+      </c>
+      <c r="L67" s="52"/>
       <c r="M67" s="48">
-        <v>3380</v>
+        <v>4940</v>
       </c>
       <c r="N67" s="48">
-        <v>2850</v>
+        <v>1510</v>
       </c>
       <c r="O67" s="57">
-        <v>1.1859649122807017</v>
+        <v>3.2715231788079469</v>
       </c>
       <c r="P67" s="52">
         <v>0</v>
       </c>
-      <c r="Q67" s="73">
-        <v>2</v>
-      </c>
-      <c r="R67" s="73">
-        <v>0</v>
+      <c r="Q67" s="48">
+        <v>4</v>
+      </c>
+      <c r="R67" s="48">
+        <v>1</v>
       </c>
       <c r="S67" s="73">
         <v>0</v>
@@ -13080,10 +13077,10 @@
       <c r="U67" s="73">
         <v>0</v>
       </c>
-      <c r="V67" s="152">
-        <v>1</v>
-      </c>
-      <c r="W67" s="152">
+      <c r="V67" s="155">
+        <v>2</v>
+      </c>
+      <c r="W67" s="151">
         <v>0</v>
       </c>
       <c r="X67" s="52">
@@ -13102,49 +13099,49 @@
         <v>0</v>
       </c>
       <c r="AC67" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="48">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AF67" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG67" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH67" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI67" s="48">
         <v>0</v>
       </c>
-      <c r="AJ67" s="59">
-        <v>1</v>
+      <c r="AJ67" s="52">
+        <v>0</v>
       </c>
       <c r="AK67" s="47">
-        <v>5</v>
-      </c>
-      <c r="AL67" s="74">
-        <v>1</v>
+        <v>7.7</v>
+      </c>
+      <c r="AL67" s="48">
+        <v>3</v>
       </c>
       <c r="AM67" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN67" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO67" s="48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN67" s="52">
+        <v>1</v>
+      </c>
+      <c r="AO67" s="52">
+        <v>1</v>
       </c>
       <c r="AP67" s="48">
         <v>0</v>
       </c>
       <c r="AQ67" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR67" s="59">
         <v>0</v>
@@ -13171,10 +13168,10 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="47">
-        <v>50.266666666666666</v>
+        <v>2.4666666666666668</v>
       </c>
       <c r="BA67" s="47">
-        <v>50.266666666666666</v>
+        <v>2.4666666666666668</v>
       </c>
       <c r="BB67" s="65"/>
       <c r="BC67" s="65"/>
@@ -13183,13 +13180,13 @@
         <v>41</v>
       </c>
       <c r="BF67" s="49">
-        <v>42032</v>
+        <v>41984</v>
       </c>
       <c r="BG67" s="135">
-        <v>43561</v>
+        <v>42060</v>
       </c>
       <c r="BH67" s="135">
-        <v>43561</v>
+        <v>42060</v>
       </c>
       <c r="BI67" s="53" t="s">
         <v>45</v>
@@ -13200,49 +13197,49 @@
     </row>
     <row r="68" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="48">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B68" s="48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C68" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E68" s="72">
-        <v>62.99722222222222</v>
-      </c>
-      <c r="F68" s="75">
-        <v>0</v>
+        <v>76.836111111111109</v>
+      </c>
+      <c r="F68" s="55">
+        <v>1</v>
       </c>
       <c r="G68" s="52">
         <v>0</v>
       </c>
       <c r="H68" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" s="48">
         <v>5</v>
       </c>
       <c r="J68" s="47">
-        <v>28.507521599929827</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="K68" s="48">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="L68" s="48">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M68" s="48">
-        <v>3630</v>
+        <v>4800</v>
       </c>
       <c r="N68" s="48">
-        <v>2350</v>
+        <v>1600</v>
       </c>
       <c r="O68" s="57">
-        <v>1.5446808510638297</v>
+        <v>3</v>
       </c>
       <c r="P68" s="52">
         <v>0</v>
@@ -13254,18 +13251,18 @@
         <v>0</v>
       </c>
       <c r="S68" s="73">
-        <v>0</v>
-      </c>
-      <c r="T68" s="73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T68" s="59">
+        <v>1</v>
       </c>
       <c r="U68" s="112">
         <v>0</v>
       </c>
-      <c r="V68" s="152">
-        <v>1</v>
-      </c>
-      <c r="W68" s="152">
+      <c r="V68" s="151">
+        <v>2</v>
+      </c>
+      <c r="W68" s="151">
         <v>0</v>
       </c>
       <c r="X68" s="39">
@@ -13284,117 +13281,123 @@
         <v>0</v>
       </c>
       <c r="AC68" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE68" s="48">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AF68" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG68" s="48">
         <v>1</v>
       </c>
       <c r="AH68" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI68" s="48">
         <v>1</v>
       </c>
-      <c r="AJ68" s="52">
-        <v>0</v>
+      <c r="AJ68" s="59">
+        <v>1</v>
       </c>
       <c r="AK68" s="47">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AL68" s="48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM68" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN68" s="52">
-        <v>1</v>
-      </c>
-      <c r="AO68" s="52">
+        <v>1</v>
+      </c>
+      <c r="AN68" s="48">
+        <v>2</v>
+      </c>
+      <c r="AO68" s="48">
         <v>1</v>
       </c>
       <c r="AP68" s="48">
         <v>0</v>
       </c>
       <c r="AQ68" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR68" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR68" s="76">
+        <v>1</v>
       </c>
       <c r="AS68" s="48">
-        <v>7</v>
-      </c>
-      <c r="AT68" s="65">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="AT68" s="62">
+        <v>0</v>
       </c>
       <c r="AU68" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV68" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW68" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX68" s="62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW68" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX68" s="65">
+        <v>1</v>
       </c>
       <c r="AY68" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ68" s="47">
-        <v>60</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="BA68" s="47">
-        <v>60</v>
-      </c>
-      <c r="BB68" s="65"/>
-      <c r="BC68" s="65"/>
-      <c r="BD68" s="65"/>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="BB68" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC68" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD68" s="65">
+        <v>1</v>
+      </c>
       <c r="BE68" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF68" s="49">
-        <v>42089</v>
-      </c>
-      <c r="BG68" s="137">
-        <v>44534</v>
-      </c>
-      <c r="BH68" s="137">
-        <v>44534</v>
+        <v>41990</v>
+      </c>
+      <c r="BG68" s="134" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH68" s="134">
+        <v>42923</v>
       </c>
       <c r="BI68" s="53" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="BJ68" s="98" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="48">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C69" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E69" s="72">
-        <v>55.338888888888889</v>
+        <v>53.802777777777777</v>
       </c>
       <c r="F69" s="75">
         <v>0</v>
@@ -13406,49 +13409,49 @@
         <v>0</v>
       </c>
       <c r="I69" s="48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69" s="47">
-        <v>26.377898098014718</v>
+        <v>35.055631763450684</v>
       </c>
       <c r="K69" s="48">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="L69" s="48">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="M69" s="48">
-        <v>3120</v>
+        <v>3380</v>
       </c>
       <c r="N69" s="48">
-        <v>900</v>
+        <v>2850</v>
       </c>
       <c r="O69" s="57">
-        <v>3.4666666666666668</v>
+        <v>1.1859649122807017</v>
       </c>
       <c r="P69" s="52">
         <v>0</v>
       </c>
-      <c r="Q69" s="48">
-        <v>4</v>
-      </c>
-      <c r="R69" s="48">
-        <v>1</v>
+      <c r="Q69" s="73">
+        <v>2</v>
+      </c>
+      <c r="R69" s="73">
+        <v>0</v>
       </c>
       <c r="S69" s="73">
-        <v>1</v>
-      </c>
-      <c r="T69" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T69" s="73">
+        <v>0</v>
       </c>
       <c r="U69" s="111">
         <v>0</v>
       </c>
-      <c r="V69" s="152">
-        <v>3</v>
-      </c>
-      <c r="W69" s="153">
-        <v>1</v>
+      <c r="V69" s="151">
+        <v>1</v>
+      </c>
+      <c r="W69" s="151">
+        <v>0</v>
       </c>
       <c r="X69" s="86">
         <v>0</v>
@@ -13463,7 +13466,7 @@
         <v>2</v>
       </c>
       <c r="AB69" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC69" s="48">
         <v>1</v>
@@ -13472,10 +13475,10 @@
         <v>1</v>
       </c>
       <c r="AE69" s="48">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AF69" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG69" s="48">
         <v>0</v>
@@ -13484,159 +13487,153 @@
         <v>0</v>
       </c>
       <c r="AI69" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ69" s="59">
         <v>1</v>
       </c>
       <c r="AK69" s="47">
-        <v>8</v>
-      </c>
-      <c r="AL69" s="48">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AL69" s="74">
+        <v>1</v>
       </c>
       <c r="AM69" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN69" s="52">
-        <v>1</v>
-      </c>
-      <c r="AO69" s="52">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AN69" s="48">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="48">
+        <v>0</v>
       </c>
       <c r="AP69" s="48">
         <v>0</v>
       </c>
       <c r="AQ69" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR69" s="76">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AR69" s="59">
+        <v>0</v>
       </c>
       <c r="AS69" s="48">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AT69" s="65">
         <v>0</v>
       </c>
       <c r="AU69" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV69" s="52">
-        <v>1</v>
-      </c>
-      <c r="AW69" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX69" s="65">
-        <v>1</v>
-      </c>
-      <c r="AY69" s="65">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AW69" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX69" s="62">
+        <v>0</v>
+      </c>
+      <c r="AY69" s="62">
+        <v>0</v>
       </c>
       <c r="AZ69" s="47">
-        <v>28.3</v>
+        <v>50.266666666666666</v>
       </c>
       <c r="BA69" s="47">
-        <v>30.733333333333334</v>
-      </c>
-      <c r="BB69" s="65">
-        <v>0</v>
-      </c>
-      <c r="BC69" s="65">
-        <v>1</v>
-      </c>
-      <c r="BD69" s="65">
-        <v>0</v>
-      </c>
+        <v>50.266666666666666</v>
+      </c>
+      <c r="BB69" s="65"/>
+      <c r="BC69" s="65"/>
+      <c r="BD69" s="65"/>
       <c r="BE69" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF69" s="49">
-        <v>42094</v>
-      </c>
-      <c r="BG69" s="134" t="s">
-        <v>64</v>
-      </c>
-      <c r="BH69" s="134">
-        <v>43030</v>
+        <v>42032</v>
+      </c>
+      <c r="BG69" s="135">
+        <v>43561</v>
+      </c>
+      <c r="BH69" s="135">
+        <v>43561</v>
       </c>
       <c r="BI69" s="53" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="BJ69" s="98" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="48">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C70" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D70" s="48" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E70" s="72">
-        <v>66.86666666666666</v>
-      </c>
-      <c r="F70" s="55">
-        <v>1</v>
+        <v>62.99722222222222</v>
+      </c>
+      <c r="F70" s="75">
+        <v>0</v>
       </c>
       <c r="G70" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="48">
         <v>1</v>
       </c>
       <c r="I70" s="48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70" s="47">
-        <v>23.068050749711649</v>
+        <v>28.507521599929827</v>
       </c>
       <c r="K70" s="48">
-        <v>10.3</v>
+        <v>13.1</v>
       </c>
       <c r="L70" s="48">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="M70" s="48">
-        <v>1680</v>
+        <v>3630</v>
       </c>
       <c r="N70" s="48">
-        <v>740</v>
+        <v>2350</v>
       </c>
       <c r="O70" s="57">
-        <v>2.2702702702702702</v>
+        <v>1.5446808510638297</v>
       </c>
       <c r="P70" s="52">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="48">
-        <v>3</v>
-      </c>
-      <c r="R70" s="48">
-        <v>1</v>
-      </c>
-      <c r="S70" s="48">
-        <v>2</v>
-      </c>
-      <c r="T70" s="59">
-        <v>1</v>
-      </c>
-      <c r="U70" s="48">
-        <v>1</v>
-      </c>
-      <c r="V70" s="152">
-        <v>4</v>
-      </c>
-      <c r="W70" s="152">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="73">
+        <v>2</v>
+      </c>
+      <c r="R70" s="73">
+        <v>0</v>
+      </c>
+      <c r="S70" s="73">
+        <v>0</v>
+      </c>
+      <c r="T70" s="73">
+        <v>0</v>
+      </c>
+      <c r="U70" s="73">
+        <v>0</v>
+      </c>
+      <c r="V70" s="151">
+        <v>1</v>
+      </c>
+      <c r="W70" s="151">
+        <v>0</v>
       </c>
       <c r="X70" s="52">
         <v>0</v>
@@ -13644,187 +13641,181 @@
       <c r="Y70" s="74">
         <v>1</v>
       </c>
-      <c r="Z70" s="52">
+      <c r="Z70" s="48">
         <v>0</v>
       </c>
       <c r="AA70" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB70" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD70" s="48">
         <v>1</v>
       </c>
       <c r="AE70" s="48">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AF70" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG70" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH70" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI70" s="48">
         <v>1</v>
       </c>
-      <c r="AJ70" s="59">
-        <v>1</v>
+      <c r="AJ70" s="52">
+        <v>0</v>
       </c>
       <c r="AK70" s="47">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AL70" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM70" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN70" s="48">
-        <v>2</v>
-      </c>
-      <c r="AO70" s="48">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="52">
+        <v>1</v>
+      </c>
+      <c r="AO70" s="52">
         <v>1</v>
       </c>
       <c r="AP70" s="48">
         <v>0</v>
       </c>
       <c r="AQ70" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR70" s="76">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR70" s="59">
+        <v>0</v>
       </c>
       <c r="AS70" s="48">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AT70" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV70" s="52">
         <v>0</v>
       </c>
-      <c r="AW70" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX70" s="65">
-        <v>1</v>
+      <c r="AW70" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX70" s="62">
+        <v>0</v>
       </c>
       <c r="AY70" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ70" s="47">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BA70" s="47">
-        <v>3.2333333333333334</v>
-      </c>
-      <c r="BB70" s="65">
-        <v>1</v>
-      </c>
-      <c r="BC70" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD70" s="65">
-        <v>0</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="BB70" s="65"/>
+      <c r="BC70" s="65"/>
+      <c r="BD70" s="65"/>
       <c r="BE70" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF70" s="49">
-        <v>42110</v>
-      </c>
-      <c r="BG70" s="134" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH70" s="134">
-        <v>42208</v>
+        <v>42089</v>
+      </c>
+      <c r="BG70" s="137">
+        <v>44534</v>
+      </c>
+      <c r="BH70" s="137">
+        <v>44534</v>
       </c>
       <c r="BI70" s="53" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="BJ70" s="98" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="48">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C71" s="48" t="s">
         <v>146</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E71" s="72">
-        <v>83.608333333333334</v>
-      </c>
-      <c r="F71" s="55">
-        <v>1</v>
+        <v>55.338888888888889</v>
+      </c>
+      <c r="F71" s="75">
+        <v>0</v>
       </c>
       <c r="G71" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="48">
         <v>4</v>
       </c>
       <c r="J71" s="47">
-        <v>23.529411764705884</v>
+        <v>26.377898098014718</v>
       </c>
       <c r="K71" s="48">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="L71" s="48">
-        <v>4.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M71" s="48">
-        <v>4640</v>
+        <v>3120</v>
       </c>
       <c r="N71" s="48">
-        <v>1440</v>
+        <v>900</v>
       </c>
       <c r="O71" s="57">
-        <v>3.2222222222222223</v>
+        <v>3.4666666666666668</v>
       </c>
       <c r="P71" s="52">
         <v>0</v>
       </c>
-      <c r="Q71" s="73">
-        <v>2</v>
-      </c>
-      <c r="R71" s="73">
-        <v>0</v>
+      <c r="Q71" s="48">
+        <v>4</v>
+      </c>
+      <c r="R71" s="48">
+        <v>1</v>
       </c>
       <c r="S71" s="73">
-        <v>0</v>
-      </c>
-      <c r="T71" s="73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T71" s="59">
+        <v>1</v>
       </c>
       <c r="U71" s="112">
         <v>0</v>
       </c>
-      <c r="V71" s="152">
-        <v>1</v>
+      <c r="V71" s="151">
+        <v>3</v>
       </c>
       <c r="W71" s="152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="39">
         <v>0</v>
@@ -13836,22 +13827,22 @@
         <v>0</v>
       </c>
       <c r="AA71" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB71" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC71" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD71" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE71" s="48">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AF71" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG71" s="48">
         <v>0</v>
@@ -13860,79 +13851,85 @@
         <v>0</v>
       </c>
       <c r="AI71" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ71" s="52">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ71" s="59">
+        <v>1</v>
       </c>
       <c r="AK71" s="47">
-        <v>1.2</v>
-      </c>
-      <c r="AL71" s="74">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="AL71" s="48">
+        <v>3</v>
       </c>
       <c r="AM71" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN71" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN71" s="52">
+        <v>1</v>
+      </c>
+      <c r="AO71" s="52">
+        <v>1</v>
       </c>
       <c r="AP71" s="48">
         <v>0</v>
       </c>
       <c r="AQ71" s="48">
-        <v>1</v>
-      </c>
-      <c r="AR71" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR71" s="76">
+        <v>1</v>
       </c>
       <c r="AS71" s="48">
-        <v>6</v>
-      </c>
-      <c r="AT71" s="62">
+        <v>15</v>
+      </c>
+      <c r="AT71" s="65">
         <v>0</v>
       </c>
       <c r="AU71" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV71" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW71" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX71" s="62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW71" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX71" s="65">
+        <v>1</v>
       </c>
       <c r="AY71" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ71" s="47">
-        <v>60</v>
+        <v>28.3</v>
       </c>
       <c r="BA71" s="47">
-        <v>60</v>
-      </c>
-      <c r="BB71" s="65"/>
-      <c r="BC71" s="65"/>
-      <c r="BD71" s="65"/>
+        <v>30.733333333333334</v>
+      </c>
+      <c r="BB71" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC71" s="65">
+        <v>1</v>
+      </c>
+      <c r="BD71" s="65">
+        <v>0</v>
+      </c>
       <c r="BE71" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF71" s="49">
-        <v>42123</v>
-      </c>
-      <c r="BG71" s="137">
-        <v>44572</v>
-      </c>
-      <c r="BH71" s="137">
-        <v>44572</v>
+        <v>42094</v>
+      </c>
+      <c r="BG71" s="134" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH71" s="134">
+        <v>43030</v>
       </c>
       <c r="BI71" s="53" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="BJ71" s="98" t="s">
         <v>43</v>
@@ -13940,19 +13937,19 @@
     </row>
     <row r="72" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="48">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E72" s="72">
-        <v>77.111111111111114</v>
+        <v>66.86666666666666</v>
       </c>
       <c r="F72" s="55">
         <v>1</v>
@@ -13961,52 +13958,52 @@
         <v>1</v>
       </c>
       <c r="H72" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" s="47">
-        <v>27.580200319349689</v>
+        <v>23.068050749711649</v>
       </c>
       <c r="K72" s="48">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="L72" s="48">
-        <v>4.0999999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="M72" s="48">
-        <v>4540</v>
+        <v>1680</v>
       </c>
       <c r="N72" s="48">
-        <v>1910</v>
+        <v>740</v>
       </c>
       <c r="O72" s="57">
-        <v>2.3769633507853403</v>
+        <v>2.2702702702702702</v>
       </c>
       <c r="P72" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="73">
-        <v>2</v>
-      </c>
-      <c r="R72" s="73">
-        <v>0</v>
-      </c>
-      <c r="S72" s="73">
-        <v>0</v>
-      </c>
-      <c r="T72" s="73">
-        <v>0</v>
-      </c>
-      <c r="U72" s="73">
-        <v>0</v>
-      </c>
-      <c r="V72" s="152">
-        <v>1</v>
-      </c>
-      <c r="W72" s="152">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q72" s="48">
+        <v>3</v>
+      </c>
+      <c r="R72" s="48">
+        <v>1</v>
+      </c>
+      <c r="S72" s="48">
+        <v>2</v>
+      </c>
+      <c r="T72" s="59">
+        <v>1</v>
+      </c>
+      <c r="U72" s="48">
+        <v>1</v>
+      </c>
+      <c r="V72" s="151">
+        <v>4</v>
+      </c>
+      <c r="W72" s="151">
+        <v>2</v>
       </c>
       <c r="X72" s="52">
         <v>0</v>
@@ -14014,26 +14011,26 @@
       <c r="Y72" s="74">
         <v>1</v>
       </c>
-      <c r="Z72" s="48">
+      <c r="Z72" s="52">
         <v>0</v>
       </c>
       <c r="AA72" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB72" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC72" s="48">
         <v>0</v>
       </c>
       <c r="AD72" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" s="48">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="AF72" s="48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG72" s="48">
         <v>0</v>
@@ -14044,8 +14041,8 @@
       <c r="AI72" s="48">
         <v>1</v>
       </c>
-      <c r="AJ72" s="52">
-        <v>0</v>
+      <c r="AJ72" s="59">
+        <v>1</v>
       </c>
       <c r="AK72" s="47">
         <v>6</v>
@@ -14057,24 +14054,24 @@
         <v>1</v>
       </c>
       <c r="AN72" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO72" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP72" s="48">
         <v>0</v>
       </c>
       <c r="AQ72" s="48">
-        <v>2</v>
-      </c>
-      <c r="AR72" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR72" s="76">
+        <v>1</v>
       </c>
       <c r="AS72" s="48">
-        <v>14</v>
-      </c>
-      <c r="AT72" s="62">
+        <v>20</v>
+      </c>
+      <c r="AT72" s="65">
         <v>0</v>
       </c>
       <c r="AU72" s="52">
@@ -14083,110 +14080,118 @@
       <c r="AV72" s="52">
         <v>0</v>
       </c>
-      <c r="AW72" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX72" s="62">
-        <v>0</v>
-      </c>
-      <c r="AY72" s="62">
-        <v>0</v>
+      <c r="AW72" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX72" s="65">
+        <v>1</v>
+      </c>
+      <c r="AY72" s="65">
+        <v>1</v>
       </c>
       <c r="AZ72" s="47">
-        <v>48.833333333333336</v>
+        <v>0</v>
       </c>
       <c r="BA72" s="47">
-        <v>48.833333333333336</v>
-      </c>
-      <c r="BB72" s="65"/>
-      <c r="BC72" s="65"/>
-      <c r="BD72" s="65"/>
+        <v>3.2333333333333334</v>
+      </c>
+      <c r="BB72" s="65">
+        <v>1</v>
+      </c>
+      <c r="BC72" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD72" s="65">
+        <v>0</v>
+      </c>
       <c r="BE72" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF72" s="49">
-        <v>42129</v>
-      </c>
-      <c r="BG72" s="135">
-        <v>43615</v>
-      </c>
-      <c r="BH72" s="135">
-        <v>43615</v>
+        <v>42110</v>
+      </c>
+      <c r="BG72" s="134" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH72" s="134">
+        <v>42208</v>
       </c>
       <c r="BI72" s="53" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="BJ72" s="98" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="48">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C73" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E73" s="72">
-        <v>79.555555555555557</v>
+        <v>83.608333333333334</v>
       </c>
       <c r="F73" s="55">
         <v>1</v>
       </c>
       <c r="G73" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="48">
         <v>1</v>
       </c>
       <c r="I73" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" s="47">
-        <v>25.566106647187731</v>
+        <v>23.529411764705884</v>
       </c>
       <c r="K73" s="48">
-        <v>9.6</v>
-      </c>
-      <c r="L73" s="52"/>
+        <v>13.3</v>
+      </c>
+      <c r="L73" s="48">
+        <v>4.7</v>
+      </c>
       <c r="M73" s="48">
-        <v>6100</v>
+        <v>4640</v>
       </c>
       <c r="N73" s="48">
-        <v>2800</v>
+        <v>1440</v>
       </c>
       <c r="O73" s="57">
-        <v>2.1785714285714284</v>
+        <v>3.2222222222222223</v>
       </c>
       <c r="P73" s="52">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="48">
-        <v>4</v>
-      </c>
-      <c r="R73" s="48">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="73">
+        <v>2</v>
+      </c>
+      <c r="R73" s="73">
+        <v>0</v>
       </c>
       <c r="S73" s="73">
-        <v>2</v>
-      </c>
-      <c r="T73" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T73" s="73">
+        <v>0</v>
       </c>
       <c r="U73" s="73">
         <v>0</v>
       </c>
-      <c r="V73" s="152">
-        <v>3</v>
-      </c>
-      <c r="W73" s="153">
-        <v>1</v>
+      <c r="V73" s="151">
+        <v>1</v>
+      </c>
+      <c r="W73" s="151">
+        <v>0</v>
       </c>
       <c r="X73" s="52">
         <v>0</v>
@@ -14198,67 +14203,67 @@
         <v>0</v>
       </c>
       <c r="AA73" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB73" s="48">
         <v>0</v>
       </c>
       <c r="AC73" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD73" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE73" s="48">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AF73" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG73" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH73" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI73" s="48">
-        <v>1</v>
-      </c>
-      <c r="AJ73" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="52">
+        <v>0</v>
       </c>
       <c r="AK73" s="47">
-        <v>7</v>
-      </c>
-      <c r="AL73" s="48">
-        <v>3</v>
+        <v>1.2</v>
+      </c>
+      <c r="AL73" s="74">
+        <v>1</v>
       </c>
       <c r="AM73" s="48">
-        <v>1</v>
-      </c>
-      <c r="AN73" s="52">
-        <v>1</v>
-      </c>
-      <c r="AO73" s="52">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AN73" s="48">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="48">
+        <v>0</v>
       </c>
       <c r="AP73" s="48">
         <v>0</v>
       </c>
       <c r="AQ73" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR73" s="76">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AR73" s="59">
+        <v>0</v>
       </c>
       <c r="AS73" s="48">
-        <v>10</v>
-      </c>
-      <c r="AT73" s="65">
+        <v>6</v>
+      </c>
+      <c r="AT73" s="62">
         <v>0</v>
       </c>
       <c r="AU73" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV73" s="52">
         <v>0</v>
@@ -14285,36 +14290,36 @@
         <v>41</v>
       </c>
       <c r="BF73" s="49">
-        <v>42131</v>
+        <v>42123</v>
       </c>
       <c r="BG73" s="137">
-        <v>45013</v>
+        <v>44572</v>
       </c>
       <c r="BH73" s="137">
-        <v>45013</v>
+        <v>44572</v>
       </c>
       <c r="BI73" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ73" s="98" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="48">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C74" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E74" s="72">
-        <v>65.836111111111109</v>
+        <v>77.111111111111114</v>
       </c>
       <c r="F74" s="55">
         <v>1</v>
@@ -14323,31 +14328,31 @@
         <v>1</v>
       </c>
       <c r="H74" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="48">
         <v>5</v>
       </c>
       <c r="J74" s="47">
-        <v>19.607156612163443</v>
+        <v>27.580200319349689</v>
       </c>
       <c r="K74" s="48">
-        <v>10.3</v>
+        <v>13.6</v>
       </c>
       <c r="L74" s="48">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M74" s="48">
-        <v>4110</v>
+        <v>4540</v>
       </c>
       <c r="N74" s="48">
-        <v>2370</v>
+        <v>1910</v>
       </c>
       <c r="O74" s="57">
-        <v>1.7341772151898733</v>
+        <v>2.3769633507853403</v>
       </c>
       <c r="P74" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="73">
         <v>2</v>
@@ -14356,18 +14361,18 @@
         <v>0</v>
       </c>
       <c r="S74" s="73">
-        <v>1</v>
-      </c>
-      <c r="T74" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T74" s="73">
+        <v>0</v>
       </c>
       <c r="U74" s="73">
         <v>0</v>
       </c>
-      <c r="V74" s="152">
-        <v>2</v>
-      </c>
-      <c r="W74" s="152">
+      <c r="V74" s="151">
+        <v>1</v>
+      </c>
+      <c r="W74" s="151">
         <v>0</v>
       </c>
       <c r="X74" s="52">
@@ -14392,25 +14397,25 @@
         <v>0</v>
       </c>
       <c r="AE74" s="48">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AF74" s="48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG74" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH74" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI74" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ74" s="52">
         <v>0</v>
       </c>
       <c r="AK74" s="47">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AL74" s="48">
         <v>3</v>
@@ -14419,28 +14424,28 @@
         <v>1</v>
       </c>
       <c r="AN74" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO74" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP74" s="48">
         <v>0</v>
       </c>
       <c r="AQ74" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR74" s="76">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR74" s="59">
+        <v>0</v>
       </c>
       <c r="AS74" s="48">
-        <v>7</v>
-      </c>
-      <c r="AT74" s="65">
+        <v>14</v>
+      </c>
+      <c r="AT74" s="62">
         <v>0</v>
       </c>
       <c r="AU74" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV74" s="52">
         <v>0</v>
@@ -14451,14 +14456,14 @@
       <c r="AX74" s="62">
         <v>0</v>
       </c>
-      <c r="AY74" s="65">
+      <c r="AY74" s="62">
         <v>0</v>
       </c>
       <c r="AZ74" s="47">
-        <v>60</v>
+        <v>48.833333333333336</v>
       </c>
       <c r="BA74" s="47">
-        <v>60</v>
+        <v>48.833333333333336</v>
       </c>
       <c r="BB74" s="65"/>
       <c r="BC74" s="65"/>
@@ -14467,88 +14472,88 @@
         <v>41</v>
       </c>
       <c r="BF74" s="49">
-        <v>41822</v>
-      </c>
-      <c r="BG74" s="137">
-        <v>44559</v>
-      </c>
-      <c r="BH74" s="137">
-        <v>44559</v>
+        <v>42129</v>
+      </c>
+      <c r="BG74" s="135">
+        <v>43615</v>
+      </c>
+      <c r="BH74" s="135">
+        <v>43615</v>
       </c>
       <c r="BI74" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ74" s="98" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="48">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E75" s="72">
-        <v>42.897222222222226</v>
-      </c>
-      <c r="F75" s="75">
-        <v>0</v>
+        <v>79.555555555555557</v>
+      </c>
+      <c r="F75" s="55">
+        <v>1</v>
       </c>
       <c r="G75" s="52">
         <v>0</v>
       </c>
       <c r="H75" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="48">
         <v>5</v>
       </c>
       <c r="J75" s="47">
-        <v>20.451843043995243</v>
+        <v>25.566106647187731</v>
       </c>
       <c r="K75" s="48">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
       <c r="L75" s="52"/>
       <c r="M75" s="48">
-        <v>2320</v>
+        <v>6100</v>
       </c>
       <c r="N75" s="48">
-        <v>1740</v>
+        <v>2800</v>
       </c>
       <c r="O75" s="57">
-        <v>1.3333333333333333</v>
+        <v>2.1785714285714284</v>
       </c>
       <c r="P75" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="73">
-        <v>2</v>
-      </c>
-      <c r="R75" s="73">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q75" s="48">
+        <v>4</v>
+      </c>
+      <c r="R75" s="48">
+        <v>1</v>
       </c>
       <c r="S75" s="73">
-        <v>0</v>
-      </c>
-      <c r="T75" s="73">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="T75" s="59">
+        <v>1</v>
       </c>
       <c r="U75" s="73">
         <v>0</v>
       </c>
-      <c r="V75" s="152">
-        <v>1</v>
+      <c r="V75" s="151">
+        <v>3</v>
       </c>
       <c r="W75" s="152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X75" s="52">
         <v>0</v>
@@ -14572,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="AE75" s="48">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF75" s="48">
         <v>2</v>
@@ -14581,22 +14586,22 @@
         <v>1</v>
       </c>
       <c r="AH75" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI75" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ75" s="52">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="59">
+        <v>1</v>
       </c>
       <c r="AK75" s="47">
-        <v>2.5</v>
-      </c>
-      <c r="AL75" s="74">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AL75" s="48">
+        <v>3</v>
       </c>
       <c r="AM75" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN75" s="52">
         <v>1</v>
@@ -14608,15 +14613,15 @@
         <v>0</v>
       </c>
       <c r="AQ75" s="48">
-        <v>1</v>
-      </c>
-      <c r="AR75" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR75" s="76">
+        <v>1</v>
       </c>
       <c r="AS75" s="48">
-        <v>9</v>
-      </c>
-      <c r="AT75" s="62">
+        <v>10</v>
+      </c>
+      <c r="AT75" s="65">
         <v>0</v>
       </c>
       <c r="AU75" s="52">
@@ -14625,64 +14630,58 @@
       <c r="AV75" s="52">
         <v>0</v>
       </c>
-      <c r="AW75" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX75" s="65">
-        <v>1</v>
+      <c r="AW75" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX75" s="62">
+        <v>0</v>
       </c>
       <c r="AY75" s="65">
         <v>0</v>
       </c>
       <c r="AZ75" s="47">
-        <v>17.466666666666665</v>
+        <v>60</v>
       </c>
       <c r="BA75" s="47">
         <v>60</v>
       </c>
-      <c r="BB75" s="65">
-        <v>1</v>
-      </c>
-      <c r="BC75" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD75" s="65">
-        <v>0</v>
-      </c>
+      <c r="BB75" s="65"/>
+      <c r="BC75" s="65"/>
+      <c r="BD75" s="65"/>
       <c r="BE75" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF75" s="49">
-        <v>42172</v>
-      </c>
-      <c r="BG75" s="134" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH75" s="134">
-        <v>44882</v>
+        <v>42131</v>
+      </c>
+      <c r="BG75" s="137">
+        <v>45013</v>
+      </c>
+      <c r="BH75" s="137">
+        <v>45013</v>
       </c>
       <c r="BI75" s="53" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="BJ75" s="98" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="48">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E76" s="72">
-        <v>50.697222222222223</v>
+        <v>42.897222222222226</v>
       </c>
       <c r="F76" s="75">
         <v>0</v>
@@ -14694,23 +14693,23 @@
         <v>0</v>
       </c>
       <c r="I76" s="48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76" s="47">
-        <v>23.051754907792983</v>
+        <v>20.451843043995243</v>
       </c>
       <c r="K76" s="48">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="L76" s="52"/>
       <c r="M76" s="48">
-        <v>3450</v>
+        <v>2320</v>
       </c>
       <c r="N76" s="48">
-        <v>1820</v>
+        <v>1740</v>
       </c>
       <c r="O76" s="57">
-        <v>1.8956043956043955</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="P76" s="52">
         <v>0</v>
@@ -14730,10 +14729,10 @@
       <c r="U76" s="73">
         <v>0</v>
       </c>
-      <c r="V76" s="152">
-        <v>1</v>
-      </c>
-      <c r="W76" s="152">
+      <c r="V76" s="151">
+        <v>1</v>
+      </c>
+      <c r="W76" s="151">
         <v>0</v>
       </c>
       <c r="X76" s="52">
@@ -14758,13 +14757,13 @@
         <v>1</v>
       </c>
       <c r="AE76" s="48">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF76" s="48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG76" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH76" s="48">
         <v>0</v>
@@ -14776,19 +14775,19 @@
         <v>0</v>
       </c>
       <c r="AK76" s="47">
-        <v>3.2</v>
-      </c>
-      <c r="AL76" s="48">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AL76" s="74">
+        <v>1</v>
       </c>
       <c r="AM76" s="48">
         <v>0</v>
       </c>
-      <c r="AN76" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO76" s="48">
-        <v>0</v>
+      <c r="AN76" s="52">
+        <v>1</v>
+      </c>
+      <c r="AO76" s="52">
+        <v>1</v>
       </c>
       <c r="AP76" s="48">
         <v>0</v>
@@ -14800,110 +14799,126 @@
         <v>0</v>
       </c>
       <c r="AS76" s="48">
-        <v>6</v>
-      </c>
-      <c r="AT76" s="65">
+        <v>9</v>
+      </c>
+      <c r="AT76" s="62">
         <v>0</v>
       </c>
       <c r="AU76" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV76" s="52">
         <v>0</v>
       </c>
-      <c r="AW76" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX76" s="62">
-        <v>0</v>
+      <c r="AW76" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX76" s="65">
+        <v>1</v>
       </c>
       <c r="AY76" s="65">
         <v>0</v>
       </c>
       <c r="AZ76" s="113">
-        <v>60</v>
+        <v>17.466666666666665</v>
       </c>
       <c r="BA76" s="113">
         <v>60</v>
       </c>
-      <c r="BB76" s="65"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
+      <c r="BB76" s="65">
+        <v>1</v>
+      </c>
+      <c r="BC76" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD76" s="65">
+        <v>0</v>
+      </c>
       <c r="BE76" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF76" s="49">
-        <v>42165</v>
-      </c>
-      <c r="BG76" s="137">
-        <v>45197</v>
-      </c>
-      <c r="BH76" s="137">
-        <v>45197</v>
+        <v>42172</v>
+      </c>
+      <c r="BG76" s="134" t="s">
+        <v>72</v>
+      </c>
+      <c r="BH76" s="134">
+        <v>44882</v>
       </c>
       <c r="BI76" s="53" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="BJ76" s="98" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="48">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="D77" s="82">
-        <v>16781</v>
+        <v>146</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>73</v>
       </c>
       <c r="E77" s="72">
-        <v>69.594444444444449</v>
-      </c>
-      <c r="F77" s="55">
-        <v>1</v>
+        <v>50.697222222222223</v>
+      </c>
+      <c r="F77" s="75">
+        <v>0</v>
       </c>
       <c r="G77" s="52">
         <v>0</v>
       </c>
-      <c r="H77" s="52">
-        <v>0</v>
-      </c>
-      <c r="I77" s="52">
-        <v>3</v>
-      </c>
-      <c r="J77" s="47"/>
-      <c r="K77" s="52"/>
+      <c r="H77" s="48">
+        <v>0</v>
+      </c>
+      <c r="I77" s="48">
+        <v>4</v>
+      </c>
+      <c r="J77" s="47">
+        <v>23.051754907792983</v>
+      </c>
+      <c r="K77" s="48">
+        <v>13.8</v>
+      </c>
       <c r="L77" s="52"/>
-      <c r="M77" s="52"/>
-      <c r="N77" s="52"/>
-      <c r="O77" s="57"/>
+      <c r="M77" s="48">
+        <v>3450</v>
+      </c>
+      <c r="N77" s="48">
+        <v>1820</v>
+      </c>
+      <c r="O77" s="57">
+        <v>1.8956043956043955</v>
+      </c>
       <c r="P77" s="52">
         <v>0</v>
       </c>
-      <c r="Q77" s="59">
-        <v>1</v>
+      <c r="Q77" s="73">
+        <v>2</v>
       </c>
       <c r="R77" s="73">
         <v>0</v>
       </c>
-      <c r="S77" s="59">
-        <v>1</v>
-      </c>
-      <c r="T77" s="59">
-        <v>1</v>
-      </c>
-      <c r="U77" s="59">
-        <v>0</v>
-      </c>
-      <c r="V77" s="155">
-        <v>2</v>
-      </c>
-      <c r="W77" s="152">
+      <c r="S77" s="73">
+        <v>0</v>
+      </c>
+      <c r="T77" s="73">
+        <v>0</v>
+      </c>
+      <c r="U77" s="73">
+        <v>0</v>
+      </c>
+      <c r="V77" s="151">
+        <v>1</v>
+      </c>
+      <c r="W77" s="151">
         <v>0</v>
       </c>
       <c r="X77" s="52">
@@ -14919,46 +14934,46 @@
         <v>2</v>
       </c>
       <c r="AB77" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC77" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD77" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="59">
-        <v>41</v>
-      </c>
-      <c r="AF77" s="59">
-        <v>2</v>
-      </c>
-      <c r="AG77" s="59">
-        <v>0</v>
-      </c>
-      <c r="AH77" s="59">
-        <v>0</v>
-      </c>
-      <c r="AI77" s="59">
-        <v>0</v>
-      </c>
-      <c r="AJ77" s="59">
-        <v>1</v>
-      </c>
-      <c r="AK77" s="83">
-        <v>4.5</v>
-      </c>
-      <c r="AL77" s="74">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AE77" s="48">
+        <v>36</v>
+      </c>
+      <c r="AF77" s="48">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="48">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="48">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="48">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="47">
+        <v>3.2</v>
+      </c>
+      <c r="AL77" s="48">
+        <v>2</v>
       </c>
       <c r="AM77" s="48">
         <v>0</v>
       </c>
-      <c r="AN77" s="52">
-        <v>1</v>
-      </c>
-      <c r="AO77" s="52">
-        <v>1</v>
+      <c r="AN77" s="48">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="48">
+        <v>0</v>
       </c>
       <c r="AP77" s="48">
         <v>0</v>
@@ -14969,8 +14984,10 @@
       <c r="AR77" s="59">
         <v>0</v>
       </c>
-      <c r="AS77" s="52"/>
-      <c r="AT77" s="62">
+      <c r="AS77" s="48">
+        <v>6</v>
+      </c>
+      <c r="AT77" s="65">
         <v>0</v>
       </c>
       <c r="AU77" s="52">
@@ -14994,95 +15011,85 @@
       <c r="BA77" s="47">
         <v>60</v>
       </c>
-      <c r="BB77" s="62"/>
-      <c r="BC77" s="62"/>
-      <c r="BD77" s="62"/>
-      <c r="BE77" s="52" t="s">
+      <c r="BB77" s="65"/>
+      <c r="BC77" s="65"/>
+      <c r="BD77" s="65"/>
+      <c r="BE77" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="BF77" s="82">
-        <v>42199</v>
-      </c>
-      <c r="BG77" s="134">
-        <v>44565</v>
-      </c>
-      <c r="BH77" s="134">
-        <v>44565</v>
-      </c>
-      <c r="BI77" s="53"/>
-      <c r="BJ77" s="50" t="s">
+      <c r="BF77" s="49">
+        <v>42165</v>
+      </c>
+      <c r="BG77" s="137">
+        <v>45197</v>
+      </c>
+      <c r="BH77" s="137">
+        <v>45197</v>
+      </c>
+      <c r="BI77" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ77" s="98" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="48">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D78" s="48" t="s">
-        <v>74</v>
+        <v>142</v>
+      </c>
+      <c r="D78" s="82">
+        <v>16781</v>
       </c>
       <c r="E78" s="72">
-        <v>54.3</v>
-      </c>
-      <c r="F78" s="75">
-        <v>0</v>
+        <v>69.594444444444449</v>
+      </c>
+      <c r="F78" s="55">
+        <v>1</v>
       </c>
       <c r="G78" s="52">
-        <v>1</v>
-      </c>
-      <c r="H78" s="48">
-        <v>0</v>
-      </c>
-      <c r="I78" s="48">
-        <v>4</v>
-      </c>
-      <c r="J78" s="47">
-        <v>18.144868631151112</v>
-      </c>
-      <c r="K78" s="48">
-        <v>10.3</v>
-      </c>
-      <c r="L78" s="48">
-        <v>3.7</v>
-      </c>
-      <c r="M78" s="48">
-        <v>4600</v>
-      </c>
-      <c r="N78" s="48">
-        <v>2700</v>
-      </c>
-      <c r="O78" s="57">
-        <v>1.7037037037037037</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H78" s="52">
+        <v>0</v>
+      </c>
+      <c r="I78" s="52">
+        <v>3</v>
+      </c>
+      <c r="J78" s="47"/>
+      <c r="K78" s="52"/>
+      <c r="L78" s="52"/>
+      <c r="M78" s="52"/>
+      <c r="N78" s="52"/>
+      <c r="O78" s="57"/>
       <c r="P78" s="52">
         <v>0</v>
       </c>
-      <c r="Q78" s="48">
-        <v>4</v>
-      </c>
-      <c r="R78" s="48">
-        <v>1</v>
-      </c>
-      <c r="S78" s="48">
-        <v>3</v>
+      <c r="Q78" s="59">
+        <v>1</v>
+      </c>
+      <c r="R78" s="73">
+        <v>0</v>
+      </c>
+      <c r="S78" s="59">
+        <v>1</v>
       </c>
       <c r="T78" s="59">
         <v>1</v>
       </c>
-      <c r="U78" s="149">
-        <v>1</v>
-      </c>
-      <c r="V78" s="152">
-        <v>4</v>
-      </c>
-      <c r="W78" s="152">
-        <v>2</v>
+      <c r="U78" s="85">
+        <v>0</v>
+      </c>
+      <c r="V78" s="154">
+        <v>2</v>
+      </c>
+      <c r="W78" s="151">
+        <v>0</v>
       </c>
       <c r="X78" s="86">
         <v>0</v>
@@ -15090,67 +15097,65 @@
       <c r="Y78" s="74">
         <v>1</v>
       </c>
-      <c r="Z78" s="52">
+      <c r="Z78" s="48">
         <v>0</v>
       </c>
       <c r="AA78" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB78" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC78" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD78" s="48">
-        <v>1</v>
-      </c>
-      <c r="AE78" s="48">
-        <v>38</v>
-      </c>
-      <c r="AF78" s="48">
-        <v>10</v>
-      </c>
-      <c r="AG78" s="48">
-        <v>1</v>
-      </c>
-      <c r="AH78" s="48">
-        <v>1</v>
-      </c>
-      <c r="AI78" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ78" s="52">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="47">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AL78" s="48">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AE78" s="59">
+        <v>41</v>
+      </c>
+      <c r="AF78" s="59">
+        <v>2</v>
+      </c>
+      <c r="AG78" s="59">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="59">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="59">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="59">
+        <v>1</v>
+      </c>
+      <c r="AK78" s="83">
+        <v>4.5</v>
+      </c>
+      <c r="AL78" s="74">
+        <v>1</v>
       </c>
       <c r="AM78" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN78" s="52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO78" s="52">
         <v>1</v>
       </c>
       <c r="AP78" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ78" s="48">
-        <v>4</v>
-      </c>
-      <c r="AR78" s="76">
-        <v>1</v>
-      </c>
-      <c r="AS78" s="48">
-        <v>9</v>
-      </c>
-      <c r="AT78" s="65">
+        <v>1</v>
+      </c>
+      <c r="AR78" s="59">
+        <v>0</v>
+      </c>
+      <c r="AS78" s="52"/>
+      <c r="AT78" s="62">
         <v>0</v>
       </c>
       <c r="AU78" s="52">
@@ -15159,64 +15164,56 @@
       <c r="AV78" s="52">
         <v>0</v>
       </c>
-      <c r="AW78" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX78" s="65">
-        <v>1</v>
+      <c r="AW78" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX78" s="62">
+        <v>0</v>
       </c>
       <c r="AY78" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ78" s="47">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BA78" s="47">
-        <v>7.3</v>
-      </c>
-      <c r="BB78" s="65">
-        <v>0</v>
-      </c>
-      <c r="BC78" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD78" s="65">
-        <v>0</v>
-      </c>
-      <c r="BE78" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB78" s="62"/>
+      <c r="BC78" s="62"/>
+      <c r="BD78" s="62"/>
+      <c r="BE78" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="BF78" s="49">
-        <v>42201</v>
-      </c>
-      <c r="BG78" s="134" t="s">
-        <v>75</v>
+      <c r="BF78" s="82">
+        <v>42199</v>
+      </c>
+      <c r="BG78" s="134">
+        <v>44565</v>
       </c>
       <c r="BH78" s="134">
-        <v>42425</v>
-      </c>
-      <c r="BI78" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="BJ78" s="98" t="s">
-        <v>43</v>
+        <v>44565</v>
+      </c>
+      <c r="BI78" s="53"/>
+      <c r="BJ78" s="50" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="48">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" s="48" t="s">
         <v>146</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E79" s="72">
-        <v>58.072222222222223</v>
+        <v>54.3</v>
       </c>
       <c r="F79" s="75">
         <v>0</v>
@@ -15231,46 +15228,46 @@
         <v>4</v>
       </c>
       <c r="J79" s="47">
-        <v>18.365472910927458</v>
+        <v>18.144868631151112</v>
       </c>
       <c r="K79" s="48">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="L79" s="48">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M79" s="48">
-        <v>4550</v>
+        <v>4600</v>
       </c>
       <c r="N79" s="48">
-        <v>1950</v>
+        <v>2700</v>
       </c>
       <c r="O79" s="57">
-        <v>2.3333333333333335</v>
+        <v>1.7037037037037037</v>
       </c>
       <c r="P79" s="52">
         <v>0</v>
       </c>
-      <c r="Q79" s="73">
-        <v>2</v>
-      </c>
-      <c r="R79" s="73">
-        <v>0</v>
-      </c>
-      <c r="S79" s="73">
+      <c r="Q79" s="48">
+        <v>4</v>
+      </c>
+      <c r="R79" s="48">
+        <v>1</v>
+      </c>
+      <c r="S79" s="48">
         <v>3</v>
       </c>
       <c r="T79" s="59">
         <v>1</v>
       </c>
-      <c r="U79" s="73">
-        <v>0</v>
-      </c>
-      <c r="V79" s="152">
-        <v>2</v>
-      </c>
-      <c r="W79" s="152">
-        <v>0</v>
+      <c r="U79" s="48">
+        <v>1</v>
+      </c>
+      <c r="V79" s="151">
+        <v>4</v>
+      </c>
+      <c r="W79" s="151">
+        <v>2</v>
       </c>
       <c r="X79" s="52">
         <v>0</v>
@@ -15278,14 +15275,14 @@
       <c r="Y79" s="74">
         <v>1</v>
       </c>
-      <c r="Z79" s="48">
+      <c r="Z79" s="52">
         <v>0</v>
       </c>
       <c r="AA79" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB79" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC79" s="48">
         <v>1</v>
@@ -15294,10 +15291,10 @@
         <v>1</v>
       </c>
       <c r="AE79" s="48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF79" s="48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AG79" s="48">
         <v>1</v>
@@ -15306,13 +15303,13 @@
         <v>1</v>
       </c>
       <c r="AI79" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ79" s="52">
         <v>0</v>
       </c>
       <c r="AK79" s="47">
-        <v>10</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AL79" s="48">
         <v>3</v>
@@ -15327,25 +15324,25 @@
         <v>1</v>
       </c>
       <c r="AP79" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ79" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR79" s="76">
         <v>1</v>
       </c>
       <c r="AS79" s="48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT79" s="65">
         <v>0</v>
       </c>
       <c r="AU79" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV79" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" s="65">
         <v>1</v>
@@ -15357,10 +15354,10 @@
         <v>1</v>
       </c>
       <c r="AZ79" s="47">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA79" s="47">
-        <v>26.833333333333332</v>
+        <v>7.3</v>
       </c>
       <c r="BB79" s="65">
         <v>0</v>
@@ -15369,22 +15366,22 @@
         <v>0</v>
       </c>
       <c r="BD79" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE79" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF79" s="49">
-        <v>42240</v>
+        <v>42201</v>
       </c>
       <c r="BG79" s="134" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="BH79" s="134">
-        <v>43058</v>
+        <v>42425</v>
       </c>
       <c r="BI79" s="53" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="BJ79" s="98" t="s">
         <v>43</v>
@@ -15392,22 +15389,22 @@
     </row>
     <row r="80" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="48">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B80" s="48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C80" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D80" s="48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E80" s="72">
-        <v>89.797222222222217</v>
-      </c>
-      <c r="F80" s="55">
-        <v>1</v>
+        <v>58.072222222222223</v>
+      </c>
+      <c r="F80" s="75">
+        <v>0</v>
       </c>
       <c r="G80" s="52">
         <v>1</v>
@@ -15416,48 +15413,48 @@
         <v>0</v>
       </c>
       <c r="I80" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J80" s="47">
-        <v>21.224489795918366</v>
+        <v>18.365472910927458</v>
       </c>
       <c r="K80" s="48">
-        <v>11.3</v>
+        <v>14.3</v>
       </c>
       <c r="L80" s="48">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M80" s="48">
-        <v>4240</v>
+        <v>4550</v>
       </c>
       <c r="N80" s="48">
-        <v>1340</v>
+        <v>1950</v>
       </c>
       <c r="O80" s="57">
-        <v>3.1641791044776117</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="P80" s="52">
         <v>0</v>
       </c>
       <c r="Q80" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80" s="73">
         <v>0</v>
       </c>
       <c r="S80" s="73">
-        <v>0</v>
-      </c>
-      <c r="T80" s="73">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T80" s="59">
+        <v>1</v>
       </c>
       <c r="U80" s="73">
         <v>0</v>
       </c>
-      <c r="V80" s="152">
-        <v>1</v>
-      </c>
-      <c r="W80" s="152">
+      <c r="V80" s="151">
+        <v>2</v>
+      </c>
+      <c r="W80" s="151">
         <v>0</v>
       </c>
       <c r="X80" s="52">
@@ -15470,103 +15467,109 @@
         <v>0</v>
       </c>
       <c r="AA80" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE80" s="48">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AF80" s="48">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI80" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ80" s="52">
         <v>0</v>
       </c>
       <c r="AK80" s="47">
-        <v>3.5</v>
-      </c>
-      <c r="AL80" s="74">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="AL80" s="48">
+        <v>3</v>
       </c>
       <c r="AM80" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN80" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO80" s="48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN80" s="52">
+        <v>3</v>
+      </c>
+      <c r="AO80" s="52">
+        <v>1</v>
       </c>
       <c r="AP80" s="48">
         <v>0</v>
       </c>
       <c r="AQ80" s="48">
-        <v>1</v>
-      </c>
-      <c r="AR80" s="59">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AR80" s="76">
+        <v>1</v>
       </c>
       <c r="AS80" s="48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT80" s="65">
         <v>0</v>
       </c>
       <c r="AU80" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV80" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW80" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX80" s="62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW80" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX80" s="65">
+        <v>1</v>
       </c>
       <c r="AY80" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ80" s="47">
-        <v>60</v>
+        <v>1.4</v>
       </c>
       <c r="BA80" s="47">
-        <v>60</v>
-      </c>
-      <c r="BB80" s="65"/>
-      <c r="BC80" s="65"/>
-      <c r="BD80" s="65"/>
+        <v>26.833333333333332</v>
+      </c>
+      <c r="BB80" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC80" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD80" s="65">
+        <v>1</v>
+      </c>
       <c r="BE80" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF80" s="49">
-        <v>42285</v>
-      </c>
-      <c r="BG80" s="137">
-        <v>44616</v>
-      </c>
-      <c r="BH80" s="137">
-        <v>44616</v>
+        <v>42240</v>
+      </c>
+      <c r="BG80" s="134" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH80" s="134">
+        <v>43058</v>
       </c>
       <c r="BI80" s="53" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="BJ80" s="98" t="s">
         <v>43</v>
@@ -15574,19 +15577,19 @@
     </row>
     <row r="81" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="48">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B81" s="48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C81" s="48" t="s">
         <v>145</v>
       </c>
       <c r="D81" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E81" s="72">
-        <v>69.463888888888889</v>
+        <v>89.797222222222217</v>
       </c>
       <c r="F81" s="55">
         <v>1</v>
@@ -15595,34 +15598,34 @@
         <v>1</v>
       </c>
       <c r="H81" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" s="48">
         <v>5</v>
       </c>
       <c r="J81" s="47">
-        <v>25.59373706198954</v>
+        <v>21.224489795918366</v>
       </c>
       <c r="K81" s="48">
-        <v>14.2</v>
+        <v>11.3</v>
       </c>
       <c r="L81" s="48">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M81" s="48">
-        <v>2830</v>
+        <v>4240</v>
       </c>
       <c r="N81" s="48">
-        <v>1920</v>
+        <v>1340</v>
       </c>
       <c r="O81" s="57">
-        <v>1.4739583333333333</v>
+        <v>3.1641791044776117</v>
       </c>
       <c r="P81" s="52">
         <v>0</v>
       </c>
       <c r="Q81" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" s="73">
         <v>0</v>
@@ -15636,10 +15639,10 @@
       <c r="U81" s="112">
         <v>0</v>
       </c>
-      <c r="V81" s="152">
-        <v>1</v>
-      </c>
-      <c r="W81" s="152">
+      <c r="V81" s="151">
+        <v>1</v>
+      </c>
+      <c r="W81" s="151">
         <v>0</v>
       </c>
       <c r="X81" s="39">
@@ -15652,7 +15655,7 @@
         <v>0</v>
       </c>
       <c r="AA81" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB81" s="48">
         <v>0</v>
@@ -15664,7 +15667,7 @@
         <v>0</v>
       </c>
       <c r="AE81" s="48">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AF81" s="48">
         <v>0</v>
@@ -15682,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="47">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AL81" s="74">
         <v>1</v>
@@ -15706,10 +15709,10 @@
         <v>0</v>
       </c>
       <c r="AS81" s="48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT81" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU81" s="52">
         <v>0</v>
@@ -15739,72 +15742,72 @@
         <v>41</v>
       </c>
       <c r="BF81" s="49">
-        <v>42270</v>
+        <v>42285</v>
       </c>
       <c r="BG81" s="137">
-        <v>44339</v>
+        <v>44616</v>
       </c>
       <c r="BH81" s="137">
-        <v>44339</v>
+        <v>44616</v>
       </c>
       <c r="BI81" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ81" s="98" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="48">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D82" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E82" s="72">
-        <v>65.666666666666671</v>
+        <v>69.463888888888889</v>
       </c>
       <c r="F82" s="55">
         <v>1</v>
       </c>
       <c r="G82" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="48">
         <v>1</v>
       </c>
       <c r="I82" s="48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="47">
-        <v>26.370238143535232</v>
+        <v>25.59373706198954</v>
       </c>
       <c r="K82" s="48">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="L82" s="48">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="M82" s="48">
-        <v>3740</v>
+        <v>2830</v>
       </c>
       <c r="N82" s="48">
-        <v>2940</v>
+        <v>1920</v>
       </c>
       <c r="O82" s="57">
-        <v>1.272108843537415</v>
+        <v>1.4739583333333333</v>
       </c>
       <c r="P82" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82" s="73">
         <v>0</v>
@@ -15818,10 +15821,10 @@
       <c r="U82" s="73">
         <v>0</v>
       </c>
-      <c r="V82" s="152">
-        <v>1</v>
-      </c>
-      <c r="W82" s="152">
+      <c r="V82" s="151">
+        <v>1</v>
+      </c>
+      <c r="W82" s="151">
         <v>0</v>
       </c>
       <c r="X82" s="52">
@@ -15840,13 +15843,13 @@
         <v>0</v>
       </c>
       <c r="AC82" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD82" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE82" s="48">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF82" s="48">
         <v>0</v>
@@ -15864,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="47">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL82" s="74">
         <v>1</v>
@@ -15888,10 +15891,10 @@
         <v>0</v>
       </c>
       <c r="AS82" s="48">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AT82" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" s="52">
         <v>0</v>
@@ -15903,16 +15906,16 @@
         <v>0</v>
       </c>
       <c r="AX82" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY82" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ82" s="47">
-        <v>20.3</v>
+        <v>60</v>
       </c>
       <c r="BA82" s="47">
-        <v>20.3</v>
+        <v>60</v>
       </c>
       <c r="BB82" s="65"/>
       <c r="BC82" s="65"/>
@@ -15921,89 +15924,89 @@
         <v>41</v>
       </c>
       <c r="BF82" s="49">
-        <v>42299</v>
-      </c>
-      <c r="BG82" s="134">
-        <v>42917</v>
-      </c>
-      <c r="BH82" s="134">
-        <v>42917</v>
+        <v>42270</v>
+      </c>
+      <c r="BG82" s="137">
+        <v>44339</v>
+      </c>
+      <c r="BH82" s="137">
+        <v>44339</v>
       </c>
       <c r="BI82" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ82" s="98" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:62" s="119" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="48">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B83" s="48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D83" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E83" s="72">
-        <v>57.024999999999999</v>
-      </c>
-      <c r="F83" s="75">
-        <v>0</v>
+        <v>65.666666666666671</v>
+      </c>
+      <c r="F83" s="55">
+        <v>1</v>
       </c>
       <c r="G83" s="52">
         <v>0</v>
       </c>
       <c r="H83" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J83" s="47">
-        <v>21.125697902519995</v>
+        <v>26.370238143535232</v>
       </c>
       <c r="K83" s="48">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="L83" s="48">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="M83" s="48">
-        <v>3820</v>
+        <v>3740</v>
       </c>
       <c r="N83" s="48">
-        <v>1620</v>
+        <v>2940</v>
       </c>
       <c r="O83" s="57">
-        <v>2.3580246913580245</v>
+        <v>1.272108843537415</v>
       </c>
       <c r="P83" s="52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R83" s="73">
         <v>0</v>
       </c>
       <c r="S83" s="73">
-        <v>1</v>
-      </c>
-      <c r="T83" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T83" s="73">
+        <v>0</v>
       </c>
       <c r="U83" s="73">
         <v>0</v>
       </c>
-      <c r="V83" s="152">
-        <v>2</v>
-      </c>
-      <c r="W83" s="152">
+      <c r="V83" s="151">
+        <v>1</v>
+      </c>
+      <c r="W83" s="151">
         <v>0</v>
       </c>
       <c r="X83" s="52">
@@ -16025,13 +16028,13 @@
         <v>1</v>
       </c>
       <c r="AD83" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE83" s="48">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF83" s="48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG83" s="48">
         <v>0</v>
@@ -16040,37 +16043,37 @@
         <v>0</v>
       </c>
       <c r="AI83" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ83" s="52">
         <v>0</v>
       </c>
       <c r="AK83" s="47">
-        <v>4.5</v>
-      </c>
-      <c r="AL83" s="48">
-        <v>3</v>
+        <v>5.2</v>
+      </c>
+      <c r="AL83" s="74">
+        <v>1</v>
       </c>
       <c r="AM83" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN83" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO83" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP83" s="48">
         <v>0</v>
       </c>
       <c r="AQ83" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR83" s="76">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AR83" s="59">
+        <v>0</v>
       </c>
       <c r="AS83" s="48">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AT83" s="65">
         <v>0</v>
@@ -16085,16 +16088,16 @@
         <v>0</v>
       </c>
       <c r="AX83" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY83" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ83" s="47">
-        <v>60</v>
+        <v>20.3</v>
       </c>
       <c r="BA83" s="47">
-        <v>60</v>
+        <v>20.3</v>
       </c>
       <c r="BB83" s="65"/>
       <c r="BC83" s="65"/>
@@ -16103,36 +16106,36 @@
         <v>41</v>
       </c>
       <c r="BF83" s="49">
-        <v>42312</v>
-      </c>
-      <c r="BG83" s="137">
-        <v>45183</v>
-      </c>
-      <c r="BH83" s="137">
-        <v>45183</v>
+        <v>42299</v>
+      </c>
+      <c r="BG83" s="134">
+        <v>42917</v>
+      </c>
+      <c r="BH83" s="134">
+        <v>42917</v>
       </c>
       <c r="BI83" s="53" t="s">
         <v>45</v>
       </c>
       <c r="BJ83" s="98" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="48">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="D84" s="49" t="s">
-        <v>83</v>
+        <v>145</v>
+      </c>
+      <c r="D84" s="48" t="s">
+        <v>82</v>
       </c>
       <c r="E84" s="72">
-        <v>54.613888888888887</v>
+        <v>57.024999999999999</v>
       </c>
       <c r="F84" s="75">
         <v>0</v>
@@ -16143,48 +16146,50 @@
       <c r="H84" s="48">
         <v>0</v>
       </c>
-      <c r="I84" s="52">
-        <v>3</v>
+      <c r="I84" s="48">
+        <v>5</v>
       </c>
       <c r="J84" s="47">
-        <v>23.124670372023203</v>
+        <v>21.125697902519995</v>
       </c>
       <c r="K84" s="48">
-        <v>9.9</v>
-      </c>
-      <c r="L84" s="52"/>
+        <v>11.4</v>
+      </c>
+      <c r="L84" s="48">
+        <v>3.6</v>
+      </c>
       <c r="M84" s="48">
-        <v>1330</v>
+        <v>3820</v>
       </c>
       <c r="N84" s="48">
-        <v>910</v>
+        <v>1620</v>
       </c>
       <c r="O84" s="57">
-        <v>1.4615384615384615</v>
+        <v>2.3580246913580245</v>
       </c>
       <c r="P84" s="52">
         <v>0</v>
       </c>
-      <c r="Q84" s="48">
-        <v>4</v>
-      </c>
-      <c r="R84" s="48">
-        <v>1</v>
-      </c>
-      <c r="S84" s="48">
-        <v>3</v>
+      <c r="Q84" s="73">
+        <v>2</v>
+      </c>
+      <c r="R84" s="73">
+        <v>0</v>
+      </c>
+      <c r="S84" s="73">
+        <v>1</v>
       </c>
       <c r="T84" s="59">
         <v>1</v>
       </c>
-      <c r="U84" s="48">
-        <v>1</v>
-      </c>
-      <c r="V84" s="152">
-        <v>4</v>
-      </c>
-      <c r="W84" s="152">
-        <v>2</v>
+      <c r="U84" s="73">
+        <v>0</v>
+      </c>
+      <c r="V84" s="151">
+        <v>2</v>
+      </c>
+      <c r="W84" s="151">
+        <v>0</v>
       </c>
       <c r="X84" s="52">
         <v>0</v>
@@ -16192,29 +16197,29 @@
       <c r="Y84" s="74">
         <v>1</v>
       </c>
-      <c r="Z84" s="52">
+      <c r="Z84" s="48">
         <v>0</v>
       </c>
       <c r="AA84" s="48">
         <v>2</v>
       </c>
       <c r="AB84" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC84" s="48">
         <v>1</v>
       </c>
       <c r="AD84" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE84" s="48">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="AF84" s="48">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AG84" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH84" s="48">
         <v>0</v>
@@ -16222,37 +16227,37 @@
       <c r="AI84" s="48">
         <v>1</v>
       </c>
-      <c r="AJ84" s="59">
-        <v>1</v>
+      <c r="AJ84" s="52">
+        <v>0</v>
       </c>
       <c r="AK84" s="47">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AL84" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM84" s="48">
         <v>1</v>
       </c>
-      <c r="AN84" s="52">
-        <v>3</v>
-      </c>
-      <c r="AO84" s="52">
+      <c r="AN84" s="48">
+        <v>2</v>
+      </c>
+      <c r="AO84" s="48">
         <v>1</v>
       </c>
       <c r="AP84" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ84" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR84" s="76">
         <v>1</v>
       </c>
       <c r="AS84" s="48">
-        <v>36</v>
-      </c>
-      <c r="AT84" s="62">
+        <v>7</v>
+      </c>
+      <c r="AT84" s="65">
         <v>0</v>
       </c>
       <c r="AU84" s="52">
@@ -16261,64 +16266,58 @@
       <c r="AV84" s="52">
         <v>0</v>
       </c>
-      <c r="AW84" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX84" s="65">
-        <v>1</v>
+      <c r="AW84" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX84" s="62">
+        <v>0</v>
       </c>
       <c r="AY84" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ84" s="47">
-        <v>2.7</v>
+        <v>60</v>
       </c>
       <c r="BA84" s="47">
-        <v>3.5666666666666669</v>
-      </c>
-      <c r="BB84" s="65">
-        <v>0</v>
-      </c>
-      <c r="BC84" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD84" s="65">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="BB84" s="65"/>
+      <c r="BC84" s="65"/>
+      <c r="BD84" s="65"/>
       <c r="BE84" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF84" s="49">
-        <v>42397</v>
-      </c>
-      <c r="BG84" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="BH84" s="136">
-        <v>42505</v>
-      </c>
-      <c r="BI84" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="BJ84" s="50" t="s">
-        <v>43</v>
+        <v>42312</v>
+      </c>
+      <c r="BG84" s="137">
+        <v>45183</v>
+      </c>
+      <c r="BH84" s="137">
+        <v>45183</v>
+      </c>
+      <c r="BI84" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ84" s="98" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="48">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B85" s="48" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C85" s="48" t="s">
         <v>146</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="E85" s="72">
-        <v>60.18611111111111</v>
+        <v>51.844444444444441</v>
       </c>
       <c r="F85" s="75">
         <v>0</v>
@@ -16333,31 +16332,31 @@
         <v>4</v>
       </c>
       <c r="J85" s="47">
-        <v>22.67573696145125</v>
+        <v>31.244992789617044</v>
       </c>
       <c r="K85" s="48">
-        <v>13.7</v>
+        <v>12.5</v>
       </c>
       <c r="L85" s="48">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M85" s="48">
-        <v>6220</v>
+        <v>2620</v>
       </c>
       <c r="N85" s="48">
-        <v>3300</v>
+        <v>1170</v>
       </c>
       <c r="O85" s="57">
-        <v>1.8848484848484848</v>
+        <v>2.2393162393162394</v>
       </c>
       <c r="P85" s="52">
         <v>0</v>
       </c>
       <c r="Q85" s="73">
-        <v>3</v>
-      </c>
-      <c r="R85" s="48">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="R85" s="73">
+        <v>0</v>
       </c>
       <c r="S85" s="73">
         <v>1</v>
@@ -16368,11 +16367,11 @@
       <c r="U85" s="73">
         <v>0</v>
       </c>
-      <c r="V85" s="152">
-        <v>3</v>
-      </c>
-      <c r="W85" s="153">
-        <v>1</v>
+      <c r="V85" s="151">
+        <v>2</v>
+      </c>
+      <c r="W85" s="151">
+        <v>0</v>
       </c>
       <c r="X85" s="52">
         <v>0</v>
@@ -16387,7 +16386,7 @@
         <v>2</v>
       </c>
       <c r="AB85" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC85" s="48">
         <v>1</v>
@@ -16396,31 +16395,31 @@
         <v>1</v>
       </c>
       <c r="AE85" s="48">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AF85" s="48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG85" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH85" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI85" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ85" s="59">
         <v>1</v>
       </c>
       <c r="AK85" s="47">
-        <v>10.5</v>
-      </c>
-      <c r="AL85" s="48">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="AL85" s="74">
+        <v>1</v>
       </c>
       <c r="AM85" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN85" s="48">
         <v>2</v>
@@ -16432,84 +16431,78 @@
         <v>0</v>
       </c>
       <c r="AQ85" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR85" s="76">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR85" s="59">
+        <v>0</v>
       </c>
       <c r="AS85" s="48">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AT85" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" s="52">
         <v>1</v>
       </c>
       <c r="AV85" s="52">
-        <v>1</v>
-      </c>
-      <c r="AW85" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX85" s="65">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AW85" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX85" s="62">
+        <v>0</v>
       </c>
       <c r="AY85" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ85" s="47">
-        <v>21.133333333333333</v>
+        <v>60</v>
       </c>
       <c r="BA85" s="47">
-        <v>22.3</v>
-      </c>
-      <c r="BB85" s="65">
-        <v>1</v>
-      </c>
-      <c r="BC85" s="65">
-        <v>0</v>
-      </c>
-      <c r="BD85" s="65">
-        <v>0</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="BB85" s="65"/>
+      <c r="BC85" s="65"/>
+      <c r="BD85" s="65"/>
       <c r="BE85" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF85" s="49">
-        <v>41857</v>
-      </c>
-      <c r="BG85" s="134" t="s">
-        <v>48</v>
-      </c>
-      <c r="BH85" s="134">
-        <v>42536</v>
+        <v>42228</v>
+      </c>
+      <c r="BG85" s="137">
+        <v>44526</v>
+      </c>
+      <c r="BH85" s="137">
+        <v>44526</v>
       </c>
       <c r="BI85" s="53" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BJ85" s="98" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="48">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B86" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="D86" s="48" t="s">
-        <v>85</v>
+        <v>142</v>
+      </c>
+      <c r="D86" s="49" t="s">
+        <v>83</v>
       </c>
       <c r="E86" s="72">
-        <v>75.37222222222222</v>
-      </c>
-      <c r="F86" s="55">
-        <v>1</v>
+        <v>54.613888888888887</v>
+      </c>
+      <c r="F86" s="75">
+        <v>0</v>
       </c>
       <c r="G86" s="52">
         <v>0</v>
@@ -16517,50 +16510,48 @@
       <c r="H86" s="48">
         <v>0</v>
       </c>
-      <c r="I86" s="48">
-        <v>5</v>
+      <c r="I86" s="52">
+        <v>3</v>
       </c>
       <c r="J86" s="47">
-        <v>28.068944344546292</v>
+        <v>23.124670372023203</v>
       </c>
       <c r="K86" s="48">
-        <v>12.5</v>
-      </c>
-      <c r="L86" s="48">
+        <v>9.9</v>
+      </c>
+      <c r="L86" s="52"/>
+      <c r="M86" s="48">
+        <v>1330</v>
+      </c>
+      <c r="N86" s="48">
+        <v>910</v>
+      </c>
+      <c r="O86" s="57">
+        <v>1.4615384615384615</v>
+      </c>
+      <c r="P86" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="48">
         <v>4</v>
       </c>
-      <c r="M86" s="48">
-        <v>1900</v>
-      </c>
-      <c r="N86" s="48">
-        <v>1590</v>
-      </c>
-      <c r="O86" s="57">
-        <v>1.1949685534591195</v>
-      </c>
-      <c r="P86" s="52">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="73">
-        <v>1</v>
-      </c>
-      <c r="R86" s="73">
-        <v>0</v>
-      </c>
-      <c r="S86" s="73">
-        <v>0</v>
-      </c>
-      <c r="T86" s="73">
-        <v>0</v>
-      </c>
-      <c r="U86" s="73">
-        <v>0</v>
-      </c>
-      <c r="V86" s="152">
-        <v>1</v>
-      </c>
-      <c r="W86" s="152">
-        <v>0</v>
+      <c r="R86" s="48">
+        <v>1</v>
+      </c>
+      <c r="S86" s="48">
+        <v>3</v>
+      </c>
+      <c r="T86" s="59">
+        <v>1</v>
+      </c>
+      <c r="U86" s="48">
+        <v>1</v>
+      </c>
+      <c r="V86" s="151">
+        <v>4</v>
+      </c>
+      <c r="W86" s="151">
+        <v>2</v>
       </c>
       <c r="X86" s="52">
         <v>0</v>
@@ -16568,67 +16559,67 @@
       <c r="Y86" s="74">
         <v>1</v>
       </c>
-      <c r="Z86" s="48">
+      <c r="Z86" s="52">
         <v>0</v>
       </c>
       <c r="AA86" s="48">
         <v>2</v>
       </c>
       <c r="AB86" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC86" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD86" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE86" s="48">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="AF86" s="48">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AG86" s="48">
         <v>1</v>
       </c>
       <c r="AH86" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI86" s="48">
-        <v>0</v>
-      </c>
-      <c r="AJ86" s="52">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ86" s="59">
+        <v>1</v>
       </c>
       <c r="AK86" s="47">
+        <v>9</v>
+      </c>
+      <c r="AL86" s="48">
         <v>4</v>
       </c>
-      <c r="AL86" s="74">
-        <v>1</v>
-      </c>
       <c r="AM86" s="48">
-        <v>0</v>
-      </c>
-      <c r="AN86" s="48">
-        <v>0</v>
-      </c>
-      <c r="AO86" s="48">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN86" s="52">
+        <v>3</v>
+      </c>
+      <c r="AO86" s="52">
+        <v>1</v>
       </c>
       <c r="AP86" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ86" s="48">
-        <v>1</v>
-      </c>
-      <c r="AR86" s="59">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AR86" s="76">
+        <v>1</v>
       </c>
       <c r="AS86" s="48">
-        <v>7</v>
-      </c>
-      <c r="AT86" s="65">
+        <v>36</v>
+      </c>
+      <c r="AT86" s="62">
         <v>0</v>
       </c>
       <c r="AU86" s="52">
@@ -16637,112 +16628,118 @@
       <c r="AV86" s="52">
         <v>0</v>
       </c>
-      <c r="AW86" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX86" s="62">
-        <v>0</v>
-      </c>
-      <c r="AY86" s="62">
-        <v>0</v>
+      <c r="AW86" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX86" s="65">
+        <v>1</v>
+      </c>
+      <c r="AY86" s="65">
+        <v>1</v>
       </c>
       <c r="AZ86" s="47">
-        <v>45.166666666666664</v>
+        <v>2.7</v>
       </c>
       <c r="BA86" s="47">
-        <v>45.166666666666664</v>
-      </c>
-      <c r="BB86" s="65"/>
-      <c r="BC86" s="65"/>
-      <c r="BD86" s="65"/>
+        <v>3.5666666666666669</v>
+      </c>
+      <c r="BB86" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC86" s="65">
+        <v>0</v>
+      </c>
+      <c r="BD86" s="65">
+        <v>1</v>
+      </c>
       <c r="BE86" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF86" s="49">
-        <v>42403</v>
-      </c>
-      <c r="BG86" s="135">
-        <v>43777</v>
-      </c>
-      <c r="BH86" s="135">
-        <v>43777</v>
-      </c>
-      <c r="BI86" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ86" s="98" t="s">
-        <v>58</v>
+        <v>42397</v>
+      </c>
+      <c r="BG86" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH86" s="136">
+        <v>42505</v>
+      </c>
+      <c r="BI86" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="BJ86" s="50" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="48">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="B87" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E87" s="72">
+        <v>75.37222222222222</v>
+      </c>
+      <c r="F87" s="55">
+        <v>1</v>
+      </c>
+      <c r="G87" s="52">
+        <v>0</v>
+      </c>
+      <c r="H87" s="48">
+        <v>0</v>
+      </c>
+      <c r="I87" s="48">
         <v>5</v>
       </c>
-      <c r="C87" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D87" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="E87" s="72">
-        <v>75.894444444444446</v>
-      </c>
-      <c r="F87" s="55">
-        <v>1</v>
-      </c>
-      <c r="G87" s="52">
-        <v>1</v>
-      </c>
-      <c r="H87" s="48">
-        <v>0</v>
-      </c>
-      <c r="I87" s="48">
+      <c r="J87" s="47">
+        <v>28.068944344546292</v>
+      </c>
+      <c r="K87" s="48">
+        <v>12.5</v>
+      </c>
+      <c r="L87" s="48">
         <v>4</v>
       </c>
-      <c r="J87" s="47">
-        <v>22.546576480360741</v>
-      </c>
-      <c r="K87" s="48">
-        <v>11.2</v>
-      </c>
-      <c r="L87" s="48">
-        <v>3.8</v>
-      </c>
       <c r="M87" s="48">
-        <v>6380</v>
+        <v>1900</v>
       </c>
       <c r="N87" s="48">
-        <v>1670</v>
+        <v>1590</v>
       </c>
       <c r="O87" s="57">
-        <v>3.8203592814371259</v>
+        <v>1.1949685534591195</v>
       </c>
       <c r="P87" s="52">
         <v>0</v>
       </c>
       <c r="Q87" s="73">
-        <v>3</v>
-      </c>
-      <c r="R87" s="48">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="R87" s="73">
+        <v>0</v>
       </c>
       <c r="S87" s="73">
-        <v>1</v>
-      </c>
-      <c r="T87" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T87" s="73">
+        <v>0</v>
       </c>
       <c r="U87" s="73">
         <v>0</v>
       </c>
-      <c r="V87" s="152">
-        <v>3</v>
-      </c>
-      <c r="W87" s="153">
-        <v>1</v>
+      <c r="V87" s="151">
+        <v>1</v>
+      </c>
+      <c r="W87" s="151">
+        <v>0</v>
       </c>
       <c r="X87" s="52">
         <v>0</v>
@@ -16757,19 +16754,19 @@
         <v>2</v>
       </c>
       <c r="AB87" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC87" s="48">
         <v>0</v>
       </c>
       <c r="AD87" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE87" s="48">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="AF87" s="48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG87" s="48">
         <v>1</v>
@@ -16778,105 +16775,99 @@
         <v>1</v>
       </c>
       <c r="AI87" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ87" s="52">
         <v>0</v>
       </c>
       <c r="AK87" s="47">
-        <v>13</v>
-      </c>
-      <c r="AL87" s="48">
         <v>4</v>
       </c>
+      <c r="AL87" s="74">
+        <v>1</v>
+      </c>
       <c r="AM87" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN87" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO87" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP87" s="48">
         <v>0</v>
       </c>
       <c r="AQ87" s="48">
-        <v>3</v>
-      </c>
-      <c r="AR87" s="76">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AR87" s="59">
+        <v>0</v>
       </c>
       <c r="AS87" s="48">
-        <v>43</v>
-      </c>
-      <c r="AT87" s="62">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AT87" s="65">
+        <v>0</v>
       </c>
       <c r="AU87" s="52">
         <v>0</v>
       </c>
       <c r="AV87" s="52">
-        <v>1</v>
-      </c>
-      <c r="AW87" s="65">
-        <v>1</v>
-      </c>
-      <c r="AX87" s="65">
-        <v>1</v>
-      </c>
-      <c r="AY87" s="65">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AW87" s="62">
+        <v>0</v>
+      </c>
+      <c r="AX87" s="62">
+        <v>0</v>
+      </c>
+      <c r="AY87" s="62">
+        <v>0</v>
       </c>
       <c r="AZ87" s="47">
-        <v>16.733333333333334</v>
+        <v>45.166666666666664</v>
       </c>
       <c r="BA87" s="47">
-        <v>21.966666666666665</v>
-      </c>
-      <c r="BB87" s="65">
-        <v>1</v>
-      </c>
-      <c r="BC87" s="65">
-        <v>1</v>
-      </c>
-      <c r="BD87" s="65">
-        <v>0</v>
-      </c>
+        <v>45.166666666666664</v>
+      </c>
+      <c r="BB87" s="65"/>
+      <c r="BC87" s="65"/>
+      <c r="BD87" s="65"/>
       <c r="BE87" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF87" s="49">
-        <v>41879</v>
-      </c>
-      <c r="BG87" s="134" t="s">
-        <v>50</v>
-      </c>
-      <c r="BH87" s="134">
-        <v>42548</v>
+        <v>42403</v>
+      </c>
+      <c r="BG87" s="135">
+        <v>43777</v>
+      </c>
+      <c r="BH87" s="135">
+        <v>43777</v>
       </c>
       <c r="BI87" s="53" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="BJ87" s="98" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:62" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="48">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B88" s="48" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C88" s="48" t="s">
         <v>146</v>
       </c>
       <c r="D88" s="48" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E88" s="72">
-        <v>51.844444444444441</v>
+        <v>43.836111111111109</v>
       </c>
       <c r="F88" s="75">
         <v>0</v>
@@ -16891,45 +16882,45 @@
         <v>4</v>
       </c>
       <c r="J88" s="47">
-        <v>31.244992789617044</v>
+        <v>25.344352617079892</v>
       </c>
       <c r="K88" s="48">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="L88" s="48">
-        <v>3.6</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M88" s="48">
-        <v>2620</v>
+        <v>5160</v>
       </c>
       <c r="N88" s="48">
-        <v>1170</v>
+        <v>1570</v>
       </c>
       <c r="O88" s="57">
-        <v>2.2393162393162394</v>
+        <v>3.2866242038216562</v>
       </c>
       <c r="P88" s="52">
         <v>0</v>
       </c>
       <c r="Q88" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R88" s="73">
         <v>0</v>
       </c>
       <c r="S88" s="73">
-        <v>1</v>
-      </c>
-      <c r="T88" s="59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T88" s="73">
+        <v>0</v>
       </c>
       <c r="U88" s="73">
         <v>0</v>
       </c>
-      <c r="V88" s="152">
-        <v>2</v>
-      </c>
-      <c r="W88" s="152">
+      <c r="V88" s="151">
+        <v>1</v>
+      </c>
+      <c r="W88" s="151">
         <v>0</v>
       </c>
       <c r="X88" s="52">
@@ -16945,19 +16936,19 @@
         <v>2</v>
       </c>
       <c r="AB88" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC88" s="48">
         <v>1</v>
       </c>
       <c r="AD88" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE88" s="48">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AF88" s="48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG88" s="48">
         <v>0</v>
@@ -16972,19 +16963,19 @@
         <v>1</v>
       </c>
       <c r="AK88" s="47">
-        <v>2</v>
-      </c>
-      <c r="AL88" s="74">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AL88" s="48">
+        <v>3</v>
       </c>
       <c r="AM88" s="48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN88" s="48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO88" s="48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP88" s="48">
         <v>0</v>
@@ -16996,52 +16987,58 @@
         <v>0</v>
       </c>
       <c r="AS88" s="48">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AT88" s="65">
         <v>0</v>
       </c>
       <c r="AU88" s="52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV88" s="52">
-        <v>0</v>
-      </c>
-      <c r="AW88" s="62">
-        <v>0</v>
-      </c>
-      <c r="AX88" s="62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW88" s="65">
+        <v>1</v>
+      </c>
+      <c r="AX88" s="65">
+        <v>1</v>
       </c>
       <c r="AY88" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ88" s="47">
-        <v>60</v>
+        <v>10.366666666666667</v>
       </c>
       <c r="BA88" s="47">
-        <v>60</v>
-      </c>
-      <c r="BB88" s="65"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
+        <v>12.866666666666667</v>
+      </c>
+      <c r="BB88" s="65">
+        <v>0</v>
+      </c>
+      <c r="BC88" s="65">
+        <v>1</v>
+      </c>
+      <c r="BD88" s="65">
+        <v>0</v>
+      </c>
       <c r="BE88" s="48" t="s">
         <v>41</v>
       </c>
       <c r="BF88" s="49">
-        <v>42228</v>
-      </c>
-      <c r="BG88" s="137">
-        <v>44526</v>
-      </c>
-      <c r="BH88" s="137">
-        <v>44526</v>
+        <v>42144</v>
+      </c>
+      <c r="BG88" s="134" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH88" s="134">
+        <v>42537</v>
       </c>
       <c r="BI88" s="53" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="BJ88" s="98" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:62" x14ac:dyDescent="0.25">
@@ -17067,8 +17064,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:BJ88">
-    <sortState ref="A2:BH88">
-      <sortCondition ref="B1:B88"/>
+    <sortState ref="A2:BJ88">
+      <sortCondition ref="A1:A88"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B2:B4">
@@ -17246,16 +17243,16 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="157" t="s">
+      <c r="A23" s="156" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="157"/>
+      <c r="B23" s="156"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="157" t="s">
+      <c r="A24" s="156" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="157"/>
+      <c r="B24" s="156"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
